--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/work/1884-csk.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/work/1884-csk.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\work\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ADFCF1A-9ED9-4783-8B86-592F5FBC6A53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DADFBA95-7118-4811-9D8B-8F9BE223D480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="2" r:id="rId1"/>
@@ -424,6 +424,7 @@
       <b/>
       <sz val="11"/>
       <name val="Carlito"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -474,7 +475,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -502,26 +503,19 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -810,10 +804,10 @@
     <col min="1" max="1" width="40.734375" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="7.68359375" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="9.26171875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.3125" style="15" customWidth="1"/>
+    <col min="6" max="6" width="5.3125" customWidth="1"/>
     <col min="7" max="8" width="7.68359375" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="9.26171875" bestFit="1" customWidth="1"/>
-    <col min="11" max="17" width="9.26171875" style="15" customWidth="1"/>
+    <col min="11" max="17" width="9.26171875" customWidth="1"/>
     <col min="19" max="20" width="7.68359375" bestFit="1" customWidth="1"/>
     <col min="21" max="22" width="9.26171875" bestFit="1" customWidth="1"/>
     <col min="23" max="24" width="7.68359375" bestFit="1" customWidth="1"/>
@@ -857,10 +851,10 @@
         <v>8</v>
       </c>
       <c r="K1" s="11"/>
-      <c r="L1" s="18" t="s">
+      <c r="L1" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="M1" s="18" t="s">
+      <c r="M1" s="15" t="s">
         <v>124</v>
       </c>
       <c r="N1" s="11"/>
@@ -884,7 +878,7 @@
       <c r="E2" s="4">
         <v>5786</v>
       </c>
-      <c r="F2" s="12"/>
+      <c r="F2" s="4"/>
       <c r="G2" s="4">
         <v>460</v>
       </c>
@@ -897,19 +891,19 @@
       <c r="J2" s="4">
         <v>3672</v>
       </c>
-      <c r="K2" s="12"/>
-      <c r="L2" s="16">
+      <c r="K2" s="4"/>
+      <c r="L2" s="13">
         <f>B2/C2-1.05</f>
         <v>1.6825775656324593E-2</v>
       </c>
-      <c r="M2" s="16">
+      <c r="M2" s="13">
         <f>D2/E2-1.05</f>
         <v>1.8268233667473099E-2</v>
       </c>
-      <c r="N2" s="12"/>
-      <c r="O2" s="12"/>
-      <c r="P2" s="12"/>
-      <c r="Q2" s="12"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="3" t="s">
@@ -927,7 +921,7 @@
       <c r="E3" s="4">
         <v>12045</v>
       </c>
-      <c r="F3" s="12"/>
+      <c r="F3" s="4"/>
       <c r="G3" s="4">
         <v>2040</v>
       </c>
@@ -940,19 +934,19 @@
       <c r="J3" s="4">
         <v>7951</v>
       </c>
-      <c r="K3" s="12"/>
-      <c r="L3" s="16">
+      <c r="K3" s="4"/>
+      <c r="L3" s="13">
         <f t="shared" ref="L3:L66" si="0">B3/C3-1.05</f>
         <v>3.3262531860662747E-2</v>
       </c>
-      <c r="M3" s="16">
+      <c r="M3" s="13">
         <f t="shared" ref="M3:M66" si="1">D3/E3-1.05</f>
         <v>-1.0377750103773842E-4</v>
       </c>
-      <c r="N3" s="12"/>
-      <c r="O3" s="12"/>
-      <c r="P3" s="12"/>
-      <c r="Q3" s="12"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="3" t="s">
@@ -970,7 +964,7 @@
       <c r="E4" s="4">
         <v>29308</v>
       </c>
-      <c r="F4" s="12"/>
+      <c r="F4" s="4"/>
       <c r="G4" s="4">
         <v>3487</v>
       </c>
@@ -983,19 +977,19 @@
       <c r="J4" s="4">
         <v>15886</v>
       </c>
-      <c r="K4" s="12"/>
-      <c r="L4" s="17">
+      <c r="K4" s="4"/>
+      <c r="L4" s="14">
         <f t="shared" si="0"/>
         <v>0.15117137764196587</v>
       </c>
-      <c r="M4" s="16">
+      <c r="M4" s="13">
         <f t="shared" si="1"/>
         <v>2.5883717756243874E-2</v>
       </c>
-      <c r="N4" s="12"/>
-      <c r="O4" s="12"/>
-      <c r="P4" s="12"/>
-      <c r="Q4" s="12"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="3" t="s">
@@ -1013,7 +1007,7 @@
       <c r="E5" s="4">
         <v>21207</v>
       </c>
-      <c r="F5" s="12"/>
+      <c r="F5" s="4"/>
       <c r="G5" s="4">
         <v>2170</v>
       </c>
@@ -1026,19 +1020,19 @@
       <c r="J5" s="4">
         <v>12242</v>
       </c>
-      <c r="K5" s="12"/>
-      <c r="L5" s="17">
+      <c r="K5" s="4"/>
+      <c r="L5" s="14">
         <f t="shared" si="0"/>
         <v>0.33910256410256401</v>
       </c>
-      <c r="M5" s="16">
+      <c r="M5" s="13">
         <f t="shared" si="1"/>
         <v>1.4365539680294193E-2</v>
       </c>
-      <c r="N5" s="12"/>
-      <c r="O5" s="12"/>
-      <c r="P5" s="12"/>
-      <c r="Q5" s="12"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="3" t="s">
@@ -1056,7 +1050,7 @@
       <c r="E6" s="4">
         <v>21292</v>
       </c>
-      <c r="F6" s="12"/>
+      <c r="F6" s="4"/>
       <c r="G6" s="4">
         <v>2115</v>
       </c>
@@ -1069,19 +1063,19 @@
       <c r="J6" s="4">
         <v>12056</v>
       </c>
-      <c r="K6" s="12"/>
-      <c r="L6" s="17">
+      <c r="K6" s="4"/>
+      <c r="L6" s="14">
         <f t="shared" si="0"/>
         <v>0.31317489616981997</v>
       </c>
-      <c r="M6" s="16">
+      <c r="M6" s="13">
         <f t="shared" si="1"/>
         <v>1.0069509674995203E-2</v>
       </c>
-      <c r="N6" s="12"/>
-      <c r="O6" s="12"/>
-      <c r="P6" s="12"/>
-      <c r="Q6" s="12"/>
+      <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="4"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="3" t="s">
@@ -1099,7 +1093,7 @@
       <c r="E7" s="4">
         <v>33861</v>
       </c>
-      <c r="F7" s="12"/>
+      <c r="F7" s="4"/>
       <c r="G7" s="4">
         <v>2952</v>
       </c>
@@ -1112,19 +1106,19 @@
       <c r="J7" s="4">
         <v>24427</v>
       </c>
-      <c r="K7" s="12"/>
-      <c r="L7" s="16">
+      <c r="K7" s="4"/>
+      <c r="L7" s="13">
         <f t="shared" si="0"/>
         <v>-1.0632570659488527E-2</v>
       </c>
-      <c r="M7" s="16">
+      <c r="M7" s="13">
         <f t="shared" si="1"/>
         <v>5.2257759664511294E-3</v>
       </c>
-      <c r="N7" s="12"/>
-      <c r="O7" s="12"/>
-      <c r="P7" s="12"/>
-      <c r="Q7" s="12"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="3" t="s">
@@ -1142,7 +1136,7 @@
       <c r="E8" s="4">
         <v>28275</v>
       </c>
-      <c r="F8" s="12"/>
+      <c r="F8" s="4"/>
       <c r="G8" s="4">
         <v>838</v>
       </c>
@@ -1155,19 +1149,19 @@
       <c r="J8" s="4">
         <v>17671</v>
       </c>
-      <c r="K8" s="12"/>
-      <c r="L8" s="16">
+      <c r="K8" s="4"/>
+      <c r="L8" s="13">
         <f t="shared" si="0"/>
         <v>-8.5547290116896324E-3</v>
       </c>
-      <c r="M8" s="16">
+      <c r="M8" s="13">
         <f t="shared" si="1"/>
         <v>2.2369584438548529E-3</v>
       </c>
-      <c r="N8" s="12"/>
-      <c r="O8" s="12"/>
-      <c r="P8" s="12"/>
-      <c r="Q8" s="12"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="4"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="3" t="s">
@@ -1185,7 +1179,7 @@
       <c r="E9" s="4">
         <v>48197</v>
       </c>
-      <c r="F9" s="12"/>
+      <c r="F9" s="4"/>
       <c r="G9" s="4">
         <v>2169</v>
       </c>
@@ -1198,19 +1192,19 @@
       <c r="J9" s="4">
         <v>27202</v>
       </c>
-      <c r="K9" s="12"/>
-      <c r="L9" s="17">
+      <c r="K9" s="4"/>
+      <c r="L9" s="14">
         <f t="shared" si="0"/>
         <v>0.31706689536878208</v>
       </c>
-      <c r="M9" s="16">
+      <c r="M9" s="13">
         <f t="shared" si="1"/>
         <v>2.3697533041475483E-2</v>
       </c>
-      <c r="N9" s="12"/>
-      <c r="O9" s="12"/>
-      <c r="P9" s="12"/>
-      <c r="Q9" s="12"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="4"/>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="4"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="3" t="s">
@@ -1228,7 +1222,7 @@
       <c r="E10" s="4">
         <v>62381</v>
       </c>
-      <c r="F10" s="12"/>
+      <c r="F10" s="4"/>
       <c r="G10" s="4">
         <v>1737</v>
       </c>
@@ -1241,19 +1235,19 @@
       <c r="J10" s="4">
         <v>36058</v>
       </c>
-      <c r="K10" s="12"/>
-      <c r="L10" s="16">
+      <c r="K10" s="4"/>
+      <c r="L10" s="13">
         <f t="shared" si="0"/>
         <v>-3.2266009852216726E-2</v>
       </c>
-      <c r="M10" s="16">
+      <c r="M10" s="13">
         <f t="shared" si="1"/>
         <v>-2.0760327663872147E-2</v>
       </c>
-      <c r="N10" s="12"/>
-      <c r="O10" s="12"/>
-      <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
+      <c r="N10" s="4"/>
+      <c r="O10" s="4"/>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="4"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="3" t="s">
@@ -1271,7 +1265,7 @@
       <c r="E11" s="4">
         <v>75195</v>
       </c>
-      <c r="F11" s="12"/>
+      <c r="F11" s="4"/>
       <c r="G11" s="4">
         <v>1211</v>
       </c>
@@ -1284,19 +1278,19 @@
       <c r="J11" s="4">
         <v>48028</v>
       </c>
-      <c r="K11" s="12"/>
-      <c r="L11" s="16">
+      <c r="K11" s="4"/>
+      <c r="L11" s="13">
         <f t="shared" si="0"/>
         <v>5.0505050505056381E-4</v>
       </c>
-      <c r="M11" s="16">
+      <c r="M11" s="13">
         <f t="shared" si="1"/>
         <v>-1.7524436465190529E-2</v>
       </c>
-      <c r="N11" s="12"/>
-      <c r="O11" s="12"/>
-      <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="3" t="s">
@@ -1314,7 +1308,7 @@
       <c r="E12" s="4">
         <v>22163</v>
       </c>
-      <c r="F12" s="12"/>
+      <c r="F12" s="4"/>
       <c r="G12" s="4">
         <v>2607</v>
       </c>
@@ -1327,19 +1321,19 @@
       <c r="J12" s="4">
         <v>15315</v>
       </c>
-      <c r="K12" s="12"/>
-      <c r="L12" s="17">
+      <c r="K12" s="4"/>
+      <c r="L12" s="14">
         <f t="shared" si="0"/>
         <v>0.39017094017094012</v>
       </c>
-      <c r="M12" s="16">
+      <c r="M12" s="13">
         <f t="shared" si="1"/>
         <v>4.3804990299147084E-2</v>
       </c>
-      <c r="N12" s="12"/>
-      <c r="O12" s="12"/>
-      <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
+      <c r="N12" s="4"/>
+      <c r="O12" s="4"/>
+      <c r="P12" s="4"/>
+      <c r="Q12" s="4"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="3" t="s">
@@ -1357,7 +1351,7 @@
       <c r="E13" s="4">
         <v>45249</v>
       </c>
-      <c r="F13" s="12"/>
+      <c r="F13" s="4"/>
       <c r="G13" s="4">
         <v>1068</v>
       </c>
@@ -1370,19 +1364,19 @@
       <c r="J13" s="4">
         <v>24382</v>
       </c>
-      <c r="K13" s="12"/>
-      <c r="L13" s="16">
+      <c r="K13" s="4"/>
+      <c r="L13" s="13">
         <f t="shared" si="0"/>
         <v>-2.3524962178517406E-2</v>
       </c>
-      <c r="M13" s="16">
+      <c r="M13" s="13">
         <f t="shared" si="1"/>
         <v>-2.2618179407279726E-2</v>
       </c>
-      <c r="N13" s="12"/>
-      <c r="O13" s="12"/>
-      <c r="P13" s="12"/>
-      <c r="Q13" s="12"/>
+      <c r="N13" s="4"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="4"/>
+      <c r="Q13" s="4"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="3" t="s">
@@ -1400,7 +1394,7 @@
       <c r="E14" s="4">
         <v>37982</v>
       </c>
-      <c r="F14" s="12"/>
+      <c r="F14" s="4"/>
       <c r="G14" s="4">
         <v>6091</v>
       </c>
@@ -1413,19 +1407,19 @@
       <c r="J14" s="4">
         <v>21940</v>
       </c>
-      <c r="K14" s="12"/>
-      <c r="L14" s="16">
+      <c r="K14" s="4"/>
+      <c r="L14" s="13">
         <f t="shared" si="0"/>
         <v>1.0758855414092938E-2</v>
       </c>
-      <c r="M14" s="16">
+      <c r="M14" s="13">
         <f t="shared" si="1"/>
         <v>-1.4243589068505536E-3</v>
       </c>
-      <c r="N14" s="12"/>
-      <c r="O14" s="12"/>
-      <c r="P14" s="12"/>
-      <c r="Q14" s="12"/>
+      <c r="N14" s="4"/>
+      <c r="O14" s="4"/>
+      <c r="P14" s="4"/>
+      <c r="Q14" s="4"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="3" t="s">
@@ -1443,7 +1437,7 @@
       <c r="E15" s="4">
         <v>45667</v>
       </c>
-      <c r="F15" s="12"/>
+      <c r="F15" s="4"/>
       <c r="G15" s="4">
         <v>3191</v>
       </c>
@@ -1456,19 +1450,19 @@
       <c r="J15" s="4">
         <v>30890</v>
       </c>
-      <c r="K15" s="12"/>
-      <c r="L15" s="16">
+      <c r="K15" s="4"/>
+      <c r="L15" s="13">
         <f t="shared" si="0"/>
         <v>-2.206703910614527E-2</v>
       </c>
-      <c r="M15" s="16">
+      <c r="M15" s="13">
         <f t="shared" si="1"/>
         <v>3.8649352924435831E-4</v>
       </c>
-      <c r="N15" s="12"/>
-      <c r="O15" s="12"/>
-      <c r="P15" s="12"/>
-      <c r="Q15" s="12"/>
+      <c r="N15" s="4"/>
+      <c r="O15" s="4"/>
+      <c r="P15" s="4"/>
+      <c r="Q15" s="4"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="3" t="s">
@@ -1486,7 +1480,7 @@
       <c r="E16" s="4">
         <v>25140</v>
       </c>
-      <c r="F16" s="12"/>
+      <c r="F16" s="4"/>
       <c r="G16" s="4">
         <v>1512</v>
       </c>
@@ -1499,19 +1493,19 @@
       <c r="J16" s="4">
         <v>21683</v>
       </c>
-      <c r="K16" s="12"/>
-      <c r="L16" s="16">
+      <c r="K16" s="4"/>
+      <c r="L16" s="13">
         <f t="shared" si="0"/>
         <v>-7.1476510067114085E-2</v>
       </c>
-      <c r="M16" s="16">
+      <c r="M16" s="13">
         <f t="shared" si="1"/>
         <v>2.1479713603818062E-3</v>
       </c>
-      <c r="N16" s="12"/>
-      <c r="O16" s="12"/>
-      <c r="P16" s="12"/>
-      <c r="Q16" s="12"/>
+      <c r="N16" s="4"/>
+      <c r="O16" s="4"/>
+      <c r="P16" s="4"/>
+      <c r="Q16" s="4"/>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="3" t="s">
@@ -1529,7 +1523,7 @@
       <c r="E17" s="4">
         <v>65354</v>
       </c>
-      <c r="F17" s="12"/>
+      <c r="F17" s="4"/>
       <c r="G17" s="4">
         <v>5189</v>
       </c>
@@ -1542,19 +1536,19 @@
       <c r="J17" s="4">
         <v>35961</v>
       </c>
-      <c r="K17" s="12"/>
-      <c r="L17" s="17">
+      <c r="K17" s="4"/>
+      <c r="L17" s="14">
         <f t="shared" si="0"/>
         <v>0.15153614960761397</v>
       </c>
-      <c r="M17" s="16">
+      <c r="M17" s="13">
         <f t="shared" si="1"/>
         <v>3.6768981240626886E-3</v>
       </c>
-      <c r="N17" s="12"/>
-      <c r="O17" s="12"/>
-      <c r="P17" s="12"/>
-      <c r="Q17" s="12"/>
+      <c r="N17" s="4"/>
+      <c r="O17" s="4"/>
+      <c r="P17" s="4"/>
+      <c r="Q17" s="4"/>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="3" t="s">
@@ -1572,7 +1566,7 @@
       <c r="E18" s="4">
         <v>22442</v>
       </c>
-      <c r="F18" s="12"/>
+      <c r="F18" s="4"/>
       <c r="G18" s="4">
         <v>1484</v>
       </c>
@@ -1585,19 +1579,19 @@
       <c r="J18" s="4">
         <v>12897</v>
       </c>
-      <c r="K18" s="12"/>
-      <c r="L18" s="17">
+      <c r="K18" s="4"/>
+      <c r="L18" s="14">
         <f t="shared" si="0"/>
         <v>0.23243327126008695</v>
       </c>
-      <c r="M18" s="16">
+      <c r="M18" s="13">
         <f t="shared" si="1"/>
         <v>2.3567418233668924E-2</v>
       </c>
-      <c r="N18" s="12"/>
-      <c r="O18" s="12"/>
-      <c r="P18" s="12"/>
-      <c r="Q18" s="12"/>
+      <c r="N18" s="4"/>
+      <c r="O18" s="4"/>
+      <c r="P18" s="4"/>
+      <c r="Q18" s="4"/>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="3" t="s">
@@ -1615,7 +1609,7 @@
       <c r="E19" s="4">
         <v>30340</v>
       </c>
-      <c r="F19" s="12"/>
+      <c r="F19" s="4"/>
       <c r="G19" s="4">
         <v>1360</v>
       </c>
@@ -1628,19 +1622,19 @@
       <c r="J19" s="4">
         <v>21977</v>
       </c>
-      <c r="K19" s="12"/>
-      <c r="L19" s="16">
+      <c r="K19" s="4"/>
+      <c r="L19" s="13">
         <f t="shared" si="0"/>
         <v>-1.1191961191961308E-2</v>
       </c>
-      <c r="M19" s="16">
+      <c r="M19" s="13">
         <f t="shared" si="1"/>
         <v>4.8121292023730611E-3</v>
       </c>
-      <c r="N19" s="12"/>
-      <c r="O19" s="12"/>
-      <c r="P19" s="12"/>
-      <c r="Q19" s="12"/>
+      <c r="N19" s="4"/>
+      <c r="O19" s="4"/>
+      <c r="P19" s="4"/>
+      <c r="Q19" s="4"/>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="3" t="s">
@@ -1658,7 +1652,7 @@
       <c r="E20" s="4">
         <v>7620</v>
       </c>
-      <c r="F20" s="12"/>
+      <c r="F20" s="4"/>
       <c r="G20" s="4">
         <v>1050</v>
       </c>
@@ -1671,19 +1665,19 @@
       <c r="J20" s="4">
         <v>4622</v>
       </c>
-      <c r="K20" s="12"/>
-      <c r="L20" s="16">
+      <c r="K20" s="4"/>
+      <c r="L20" s="13">
         <f t="shared" si="0"/>
         <v>-5.3203997648443302E-3</v>
       </c>
-      <c r="M20" s="16">
+      <c r="M20" s="13">
         <f t="shared" si="1"/>
         <v>2.5196850393700787E-2</v>
       </c>
-      <c r="N20" s="12"/>
-      <c r="O20" s="12"/>
-      <c r="P20" s="12"/>
-      <c r="Q20" s="12"/>
+      <c r="N20" s="4"/>
+      <c r="O20" s="4"/>
+      <c r="P20" s="4"/>
+      <c r="Q20" s="4"/>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="3" t="s">
@@ -1701,7 +1695,7 @@
       <c r="E21" s="4">
         <v>54762</v>
       </c>
-      <c r="F21" s="12"/>
+      <c r="F21" s="4"/>
       <c r="G21" s="4">
         <v>4510</v>
       </c>
@@ -1714,19 +1708,19 @@
       <c r="J21" s="4">
         <v>44838</v>
       </c>
-      <c r="K21" s="12"/>
-      <c r="L21" s="16">
+      <c r="K21" s="4"/>
+      <c r="L21" s="13">
         <f t="shared" si="0"/>
         <v>-2.7286077932249908E-2</v>
       </c>
-      <c r="M21" s="17">
+      <c r="M21" s="14">
         <f t="shared" si="1"/>
         <v>-6.0646068441620127E-2</v>
       </c>
-      <c r="N21" s="12"/>
-      <c r="O21" s="12"/>
-      <c r="P21" s="12"/>
-      <c r="Q21" s="12"/>
+      <c r="N21" s="4"/>
+      <c r="O21" s="4"/>
+      <c r="P21" s="4"/>
+      <c r="Q21" s="4"/>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="3" t="s">
@@ -1744,7 +1738,7 @@
       <c r="E22" s="4">
         <v>14027</v>
       </c>
-      <c r="F22" s="12"/>
+      <c r="F22" s="4"/>
       <c r="G22" s="4">
         <v>3360</v>
       </c>
@@ -1757,19 +1751,19 @@
       <c r="J22" s="4">
         <v>9336</v>
       </c>
-      <c r="K22" s="12"/>
-      <c r="L22" s="16">
+      <c r="K22" s="4"/>
+      <c r="L22" s="13">
         <f t="shared" si="0"/>
         <v>4.269300284017552E-2</v>
       </c>
-      <c r="M22" s="16">
+      <c r="M22" s="13">
         <f t="shared" si="1"/>
         <v>4.894132743993751E-3</v>
       </c>
-      <c r="N22" s="12"/>
-      <c r="O22" s="12"/>
-      <c r="P22" s="12"/>
-      <c r="Q22" s="12"/>
+      <c r="N22" s="4"/>
+      <c r="O22" s="4"/>
+      <c r="P22" s="4"/>
+      <c r="Q22" s="4"/>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="3" t="s">
@@ -1787,7 +1781,7 @@
       <c r="E23" s="4">
         <v>30206</v>
       </c>
-      <c r="F23" s="12"/>
+      <c r="F23" s="4"/>
       <c r="G23" s="4">
         <v>2239</v>
       </c>
@@ -1800,19 +1794,19 @@
       <c r="J23" s="4">
         <v>17699</v>
       </c>
-      <c r="K23" s="12"/>
-      <c r="L23" s="17">
+      <c r="K23" s="4"/>
+      <c r="L23" s="14">
         <f t="shared" si="0"/>
         <v>0.47085308056872033</v>
       </c>
-      <c r="M23" s="16">
+      <c r="M23" s="13">
         <f t="shared" si="1"/>
         <v>2.3098059988081898E-2</v>
       </c>
-      <c r="N23" s="12"/>
-      <c r="O23" s="12"/>
-      <c r="P23" s="12"/>
-      <c r="Q23" s="12"/>
+      <c r="N23" s="4"/>
+      <c r="O23" s="4"/>
+      <c r="P23" s="4"/>
+      <c r="Q23" s="4"/>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="3" t="s">
@@ -1830,7 +1824,7 @@
       <c r="E24" s="4">
         <v>26228</v>
       </c>
-      <c r="F24" s="12"/>
+      <c r="F24" s="4"/>
       <c r="G24" s="4">
         <v>1408</v>
       </c>
@@ -1843,19 +1837,19 @@
       <c r="J24" s="4">
         <v>16146</v>
       </c>
-      <c r="K24" s="12"/>
-      <c r="L24" s="17">
+      <c r="K24" s="4"/>
+      <c r="L24" s="14">
         <f t="shared" si="0"/>
         <v>0.2725352112676056</v>
       </c>
-      <c r="M24" s="16">
+      <c r="M24" s="13">
         <f t="shared" si="1"/>
         <v>2.7779472319658272E-2</v>
       </c>
-      <c r="N24" s="12"/>
-      <c r="O24" s="12"/>
-      <c r="P24" s="12"/>
-      <c r="Q24" s="12"/>
+      <c r="N24" s="4"/>
+      <c r="O24" s="4"/>
+      <c r="P24" s="4"/>
+      <c r="Q24" s="4"/>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="3" t="s">
@@ -1873,7 +1867,7 @@
       <c r="E25" s="4">
         <v>30710</v>
       </c>
-      <c r="F25" s="12"/>
+      <c r="F25" s="4"/>
       <c r="G25" s="4">
         <v>14517</v>
       </c>
@@ -1886,19 +1880,19 @@
       <c r="J25" s="4">
         <v>24370</v>
       </c>
-      <c r="K25" s="12"/>
-      <c r="L25" s="16">
+      <c r="K25" s="4"/>
+      <c r="L25" s="13">
         <f t="shared" si="0"/>
         <v>-3.5124596356546078E-3</v>
       </c>
-      <c r="M25" s="16">
+      <c r="M25" s="13">
         <f t="shared" si="1"/>
         <v>-1.2211006186910733E-3</v>
       </c>
-      <c r="N25" s="12"/>
-      <c r="O25" s="12"/>
-      <c r="P25" s="12"/>
-      <c r="Q25" s="12"/>
+      <c r="N25" s="4"/>
+      <c r="O25" s="4"/>
+      <c r="P25" s="4"/>
+      <c r="Q25" s="4"/>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="3" t="s">
@@ -1916,7 +1910,7 @@
       <c r="E26" s="4">
         <v>37601</v>
       </c>
-      <c r="F26" s="12"/>
+      <c r="F26" s="4"/>
       <c r="G26" s="4">
         <v>2192</v>
       </c>
@@ -1929,19 +1923,19 @@
       <c r="J26" s="4">
         <v>27936</v>
       </c>
-      <c r="K26" s="12"/>
-      <c r="L26" s="16">
+      <c r="K26" s="4"/>
+      <c r="L26" s="13">
         <f t="shared" si="0"/>
         <v>7.7492596248764922E-3</v>
       </c>
-      <c r="M26" s="16">
+      <c r="M26" s="13">
         <f t="shared" si="1"/>
         <v>2.4720087231722143E-3</v>
       </c>
-      <c r="N26" s="12"/>
-      <c r="O26" s="12"/>
-      <c r="P26" s="12"/>
-      <c r="Q26" s="12"/>
+      <c r="N26" s="4"/>
+      <c r="O26" s="4"/>
+      <c r="P26" s="4"/>
+      <c r="Q26" s="4"/>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="3" t="s">
@@ -1959,7 +1953,7 @@
       <c r="E27" s="4">
         <v>25128</v>
       </c>
-      <c r="F27" s="12"/>
+      <c r="F27" s="4"/>
       <c r="G27" s="4">
         <v>1070</v>
       </c>
@@ -1972,19 +1966,19 @@
       <c r="J27" s="4">
         <v>17339</v>
       </c>
-      <c r="K27" s="12"/>
-      <c r="L27" s="16">
+      <c r="K27" s="4"/>
+      <c r="L27" s="13">
         <f t="shared" si="0"/>
         <v>1.0434372049102913E-2</v>
       </c>
-      <c r="M27" s="16">
+      <c r="M27" s="13">
         <f t="shared" si="1"/>
         <v>3.5259471505888484E-3</v>
       </c>
-      <c r="N27" s="12"/>
-      <c r="O27" s="12"/>
-      <c r="P27" s="12"/>
-      <c r="Q27" s="12"/>
+      <c r="N27" s="4"/>
+      <c r="O27" s="4"/>
+      <c r="P27" s="4"/>
+      <c r="Q27" s="4"/>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="3" t="s">
@@ -2002,7 +1996,7 @@
       <c r="E28" s="4">
         <v>7879</v>
       </c>
-      <c r="F28" s="12"/>
+      <c r="F28" s="4"/>
       <c r="G28" s="4">
         <v>439</v>
       </c>
@@ -2015,19 +2009,19 @@
       <c r="J28" s="4">
         <v>6427</v>
       </c>
-      <c r="K28" s="12"/>
-      <c r="L28" s="16">
+      <c r="K28" s="4"/>
+      <c r="L28" s="13">
         <f t="shared" si="0"/>
         <v>8.2625994694960125E-2</v>
       </c>
-      <c r="M28" s="16">
+      <c r="M28" s="13">
         <f t="shared" si="1"/>
         <v>-2.7662139865465285E-2</v>
       </c>
-      <c r="N28" s="12"/>
-      <c r="O28" s="12"/>
-      <c r="P28" s="12"/>
-      <c r="Q28" s="12"/>
+      <c r="N28" s="4"/>
+      <c r="O28" s="4"/>
+      <c r="P28" s="4"/>
+      <c r="Q28" s="4"/>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="3" t="s">
@@ -2045,7 +2039,7 @@
       <c r="E29" s="4">
         <v>33287</v>
       </c>
-      <c r="F29" s="12"/>
+      <c r="F29" s="4"/>
       <c r="G29" s="4">
         <v>3294</v>
       </c>
@@ -2058,19 +2052,19 @@
       <c r="J29" s="4">
         <v>23456</v>
       </c>
-      <c r="K29" s="12"/>
-      <c r="L29" s="16">
+      <c r="K29" s="4"/>
+      <c r="L29" s="13">
         <f t="shared" si="0"/>
         <v>2.9388415172008298E-2</v>
       </c>
-      <c r="M29" s="16">
+      <c r="M29" s="13">
         <f t="shared" si="1"/>
         <v>-1.2988554090185511E-2</v>
       </c>
-      <c r="N29" s="12"/>
-      <c r="O29" s="12"/>
-      <c r="P29" s="12"/>
-      <c r="Q29" s="12"/>
+      <c r="N29" s="4"/>
+      <c r="O29" s="4"/>
+      <c r="P29" s="4"/>
+      <c r="Q29" s="4"/>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="3" t="s">
@@ -2088,7 +2082,7 @@
       <c r="E30" s="4">
         <v>45603</v>
       </c>
-      <c r="F30" s="12"/>
+      <c r="F30" s="4"/>
       <c r="G30" s="4">
         <v>3489</v>
       </c>
@@ -2101,19 +2095,19 @@
       <c r="J30" s="4">
         <v>34274</v>
       </c>
-      <c r="K30" s="12"/>
-      <c r="L30" s="16">
+      <c r="K30" s="4"/>
+      <c r="L30" s="13">
         <f t="shared" si="0"/>
         <v>-8.0662393162393986E-3</v>
       </c>
-      <c r="M30" s="16">
+      <c r="M30" s="13">
         <f t="shared" si="1"/>
         <v>2.9351139179438768E-3</v>
       </c>
-      <c r="N30" s="12"/>
-      <c r="O30" s="12"/>
-      <c r="P30" s="12"/>
-      <c r="Q30" s="12"/>
+      <c r="N30" s="4"/>
+      <c r="O30" s="4"/>
+      <c r="P30" s="4"/>
+      <c r="Q30" s="4"/>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="3" t="s">
@@ -2131,7 +2125,7 @@
       <c r="E31" s="4">
         <v>35924</v>
       </c>
-      <c r="F31" s="12"/>
+      <c r="F31" s="4"/>
       <c r="G31" s="4">
         <v>2883</v>
       </c>
@@ -2144,19 +2138,19 @@
       <c r="J31" s="4">
         <v>25043</v>
       </c>
-      <c r="K31" s="12"/>
-      <c r="L31" s="16">
+      <c r="K31" s="4"/>
+      <c r="L31" s="13">
         <f t="shared" si="0"/>
         <v>6.1111111111111116E-2</v>
       </c>
-      <c r="M31" s="16">
+      <c r="M31" s="13">
         <f t="shared" si="1"/>
         <v>-9.5256652933972674E-3</v>
       </c>
-      <c r="N31" s="12"/>
-      <c r="O31" s="12"/>
-      <c r="P31" s="12"/>
-      <c r="Q31" s="12"/>
+      <c r="N31" s="4"/>
+      <c r="O31" s="4"/>
+      <c r="P31" s="4"/>
+      <c r="Q31" s="4"/>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="3" t="s">
@@ -2174,7 +2168,7 @@
       <c r="E32" s="4">
         <v>69376</v>
       </c>
-      <c r="F32" s="12"/>
+      <c r="F32" s="4"/>
       <c r="G32" s="4">
         <v>3623</v>
       </c>
@@ -2187,19 +2181,19 @@
       <c r="J32" s="4">
         <v>53815</v>
       </c>
-      <c r="K32" s="12"/>
-      <c r="L32" s="16">
+      <c r="K32" s="4"/>
+      <c r="L32" s="13">
         <f t="shared" si="0"/>
         <v>-3.6809815950920255E-2</v>
       </c>
-      <c r="M32" s="16">
+      <c r="M32" s="13">
         <f t="shared" si="1"/>
         <v>-4.1195802583027241E-3</v>
       </c>
-      <c r="N32" s="12"/>
-      <c r="O32" s="12"/>
-      <c r="P32" s="12"/>
-      <c r="Q32" s="12"/>
+      <c r="N32" s="4"/>
+      <c r="O32" s="4"/>
+      <c r="P32" s="4"/>
+      <c r="Q32" s="4"/>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="3" t="s">
@@ -2217,7 +2211,7 @@
       <c r="E33" s="4">
         <v>53823</v>
       </c>
-      <c r="F33" s="12"/>
+      <c r="F33" s="4"/>
       <c r="G33" s="4">
         <v>2335</v>
       </c>
@@ -2230,19 +2224,19 @@
       <c r="J33" s="4">
         <v>31182</v>
       </c>
-      <c r="K33" s="12"/>
-      <c r="L33" s="17">
+      <c r="K33" s="4"/>
+      <c r="L33" s="14">
         <f t="shared" si="0"/>
         <v>0.19145534729878722</v>
       </c>
-      <c r="M33" s="16">
+      <c r="M33" s="13">
         <f t="shared" si="1"/>
         <v>1.3002805492075886E-2</v>
       </c>
-      <c r="N33" s="12"/>
-      <c r="O33" s="12"/>
-      <c r="P33" s="12"/>
-      <c r="Q33" s="12"/>
+      <c r="N33" s="4"/>
+      <c r="O33" s="4"/>
+      <c r="P33" s="4"/>
+      <c r="Q33" s="4"/>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="3" t="s">
@@ -2260,7 +2254,7 @@
       <c r="E34" s="4">
         <v>54695</v>
       </c>
-      <c r="F34" s="12"/>
+      <c r="F34" s="4"/>
       <c r="G34" s="4">
         <v>3000</v>
       </c>
@@ -2273,19 +2267,19 @@
       <c r="J34" s="4">
         <v>29681</v>
       </c>
-      <c r="K34" s="12"/>
-      <c r="L34" s="16">
+      <c r="K34" s="4"/>
+      <c r="L34" s="13">
         <f t="shared" si="0"/>
         <v>-1.9084712755598865E-2</v>
       </c>
-      <c r="M34" s="16">
+      <c r="M34" s="13">
         <f t="shared" si="1"/>
         <v>-9.6855288417589946E-3</v>
       </c>
-      <c r="N34" s="12"/>
-      <c r="O34" s="12"/>
-      <c r="P34" s="12"/>
-      <c r="Q34" s="12"/>
+      <c r="N34" s="4"/>
+      <c r="O34" s="4"/>
+      <c r="P34" s="4"/>
+      <c r="Q34" s="4"/>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="3" t="s">
@@ -2303,7 +2297,7 @@
       <c r="E35" s="4">
         <v>20740</v>
       </c>
-      <c r="F35" s="12"/>
+      <c r="F35" s="4"/>
       <c r="G35" s="4">
         <v>808</v>
       </c>
@@ -2316,19 +2310,19 @@
       <c r="J35" s="4">
         <v>13822</v>
       </c>
-      <c r="K35" s="12"/>
-      <c r="L35" s="16">
+      <c r="K35" s="4"/>
+      <c r="L35" s="13">
         <f t="shared" si="0"/>
         <v>-1.9362745098039369E-2</v>
       </c>
-      <c r="M35" s="16">
+      <c r="M35" s="13">
         <f t="shared" si="1"/>
         <v>-1.017357762777249E-2</v>
       </c>
-      <c r="N35" s="12"/>
-      <c r="O35" s="12"/>
-      <c r="P35" s="12"/>
-      <c r="Q35" s="12"/>
+      <c r="N35" s="4"/>
+      <c r="O35" s="4"/>
+      <c r="P35" s="4"/>
+      <c r="Q35" s="4"/>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="3" t="s">
@@ -2346,7 +2340,7 @@
       <c r="E36" s="4">
         <v>40475</v>
       </c>
-      <c r="F36" s="12"/>
+      <c r="F36" s="4"/>
       <c r="G36" s="4">
         <v>2109</v>
       </c>
@@ -2359,19 +2353,19 @@
       <c r="J36" s="4">
         <v>29876</v>
       </c>
-      <c r="K36" s="12"/>
-      <c r="L36" s="16">
+      <c r="K36" s="4"/>
+      <c r="L36" s="13">
         <f t="shared" si="0"/>
         <v>3.4519981626090823E-2</v>
       </c>
-      <c r="M36" s="16">
+      <c r="M36" s="13">
         <f t="shared" si="1"/>
         <v>9.9382334774551495E-3</v>
       </c>
-      <c r="N36" s="12"/>
-      <c r="O36" s="12"/>
-      <c r="P36" s="12"/>
-      <c r="Q36" s="12"/>
+      <c r="N36" s="4"/>
+      <c r="O36" s="4"/>
+      <c r="P36" s="4"/>
+      <c r="Q36" s="4"/>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="3" t="s">
@@ -2389,7 +2383,7 @@
       <c r="E37" s="4">
         <v>72103</v>
       </c>
-      <c r="F37" s="12"/>
+      <c r="F37" s="4"/>
       <c r="G37" s="4">
         <v>3209</v>
       </c>
@@ -2402,19 +2396,19 @@
       <c r="J37" s="4">
         <v>45737</v>
       </c>
-      <c r="K37" s="12"/>
-      <c r="L37" s="16">
+      <c r="K37" s="4"/>
+      <c r="L37" s="13">
         <f t="shared" si="0"/>
         <v>2.4096943501080492E-2</v>
       </c>
-      <c r="M37" s="16">
+      <c r="M37" s="13">
         <f t="shared" si="1"/>
         <v>-1.0209700012482115E-2</v>
       </c>
-      <c r="N37" s="12"/>
-      <c r="O37" s="12"/>
-      <c r="P37" s="12"/>
-      <c r="Q37" s="12"/>
+      <c r="N37" s="4"/>
+      <c r="O37" s="4"/>
+      <c r="P37" s="4"/>
+      <c r="Q37" s="4"/>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="3" t="s">
@@ -2432,7 +2426,7 @@
       <c r="E38" s="4">
         <v>12822</v>
       </c>
-      <c r="F38" s="12"/>
+      <c r="F38" s="4"/>
       <c r="G38" s="4">
         <v>18155</v>
       </c>
@@ -2445,19 +2439,19 @@
       <c r="J38" s="4">
         <v>10928</v>
       </c>
-      <c r="K38" s="12"/>
-      <c r="L38" s="16">
+      <c r="K38" s="4"/>
+      <c r="L38" s="13">
         <f t="shared" si="0"/>
         <v>-5.4776395871924954E-3</v>
       </c>
-      <c r="M38" s="16">
+      <c r="M38" s="13">
         <f t="shared" si="1"/>
         <v>-1.0216814849477451E-3</v>
       </c>
-      <c r="N38" s="12"/>
-      <c r="O38" s="12"/>
-      <c r="P38" s="12"/>
-      <c r="Q38" s="12"/>
+      <c r="N38" s="4"/>
+      <c r="O38" s="4"/>
+      <c r="P38" s="4"/>
+      <c r="Q38" s="4"/>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="3" t="s">
@@ -2475,7 +2469,7 @@
       <c r="E39" s="4">
         <v>56066</v>
       </c>
-      <c r="F39" s="12"/>
+      <c r="F39" s="4"/>
       <c r="G39" s="4">
         <v>5607</v>
       </c>
@@ -2488,19 +2482,19 @@
       <c r="J39" s="4">
         <v>34045</v>
       </c>
-      <c r="K39" s="12"/>
-      <c r="L39" s="16">
+      <c r="K39" s="4"/>
+      <c r="L39" s="13">
         <f t="shared" si="0"/>
         <v>-2.551449601922795E-2</v>
       </c>
-      <c r="M39" s="16">
+      <c r="M39" s="13">
         <f t="shared" si="1"/>
         <v>-2.7521135804231545E-3</v>
       </c>
-      <c r="N39" s="12"/>
-      <c r="O39" s="12"/>
-      <c r="P39" s="12"/>
-      <c r="Q39" s="12"/>
+      <c r="N39" s="4"/>
+      <c r="O39" s="4"/>
+      <c r="P39" s="4"/>
+      <c r="Q39" s="4"/>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="3" t="s">
@@ -2518,7 +2512,7 @@
       <c r="E40" s="4">
         <v>35198</v>
       </c>
-      <c r="F40" s="12"/>
+      <c r="F40" s="4"/>
       <c r="G40" s="4">
         <v>1995</v>
       </c>
@@ -2531,19 +2525,19 @@
       <c r="J40" s="4">
         <v>25463</v>
       </c>
-      <c r="K40" s="12"/>
-      <c r="L40" s="16">
+      <c r="K40" s="4"/>
+      <c r="L40" s="13">
         <f t="shared" si="0"/>
         <v>-1.7304189435336514E-3</v>
       </c>
-      <c r="M40" s="16">
+      <c r="M40" s="13">
         <f t="shared" si="1"/>
         <v>-1.3407011762031962E-2</v>
       </c>
-      <c r="N40" s="12"/>
-      <c r="O40" s="12"/>
-      <c r="P40" s="12"/>
-      <c r="Q40" s="12"/>
+      <c r="N40" s="4"/>
+      <c r="O40" s="4"/>
+      <c r="P40" s="4"/>
+      <c r="Q40" s="4"/>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="3" t="s">
@@ -2561,7 +2555,7 @@
       <c r="E41" s="4">
         <v>31126</v>
       </c>
-      <c r="F41" s="12"/>
+      <c r="F41" s="4"/>
       <c r="G41" s="4">
         <v>1641</v>
       </c>
@@ -2574,19 +2568,19 @@
       <c r="J41" s="4">
         <v>23855</v>
       </c>
-      <c r="K41" s="12"/>
-      <c r="L41" s="17">
+      <c r="K41" s="4"/>
+      <c r="L41" s="14">
         <f t="shared" si="0"/>
         <v>7.9802095459837075E-2</v>
       </c>
-      <c r="M41" s="16">
+      <c r="M41" s="13">
         <f t="shared" si="1"/>
         <v>-1.5173809676797489E-2</v>
       </c>
-      <c r="N41" s="12"/>
-      <c r="O41" s="12"/>
-      <c r="P41" s="12"/>
-      <c r="Q41" s="12"/>
+      <c r="N41" s="4"/>
+      <c r="O41" s="4"/>
+      <c r="P41" s="4"/>
+      <c r="Q41" s="4"/>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="3" t="s">
@@ -2604,7 +2598,7 @@
       <c r="E42" s="4">
         <v>19363</v>
       </c>
-      <c r="F42" s="12"/>
+      <c r="F42" s="4"/>
       <c r="G42" s="4">
         <v>3366</v>
       </c>
@@ -2617,19 +2611,19 @@
       <c r="J42" s="4">
         <v>10079</v>
       </c>
-      <c r="K42" s="12"/>
-      <c r="L42" s="16">
+      <c r="K42" s="4"/>
+      <c r="L42" s="13">
         <f t="shared" si="0"/>
         <v>1.9352254520485168E-2</v>
       </c>
-      <c r="M42" s="16">
+      <c r="M42" s="13">
         <f t="shared" si="1"/>
         <v>3.092754221969729E-2</v>
       </c>
-      <c r="N42" s="12"/>
-      <c r="O42" s="12"/>
-      <c r="P42" s="12"/>
-      <c r="Q42" s="12"/>
+      <c r="N42" s="4"/>
+      <c r="O42" s="4"/>
+      <c r="P42" s="4"/>
+      <c r="Q42" s="4"/>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="3" t="s">
@@ -2647,7 +2641,7 @@
       <c r="E43" s="4">
         <v>61817</v>
       </c>
-      <c r="F43" s="12"/>
+      <c r="F43" s="4"/>
       <c r="G43" s="4">
         <v>2643</v>
       </c>
@@ -2660,19 +2654,19 @@
       <c r="J43" s="4">
         <v>38667</v>
       </c>
-      <c r="K43" s="12"/>
-      <c r="L43" s="16">
+      <c r="K43" s="4"/>
+      <c r="L43" s="13">
         <f t="shared" si="0"/>
         <v>-3.6124876114965287E-2</v>
       </c>
-      <c r="M43" s="16">
+      <c r="M43" s="13">
         <f t="shared" si="1"/>
         <v>3.8201465616254371E-3</v>
       </c>
-      <c r="N43" s="12"/>
-      <c r="O43" s="12"/>
-      <c r="P43" s="12"/>
-      <c r="Q43" s="12"/>
+      <c r="N43" s="4"/>
+      <c r="O43" s="4"/>
+      <c r="P43" s="4"/>
+      <c r="Q43" s="4"/>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="3" t="s">
@@ -2690,7 +2684,7 @@
       <c r="E44" s="4">
         <v>38073</v>
       </c>
-      <c r="F44" s="12"/>
+      <c r="F44" s="4"/>
       <c r="G44" s="4">
         <v>2221</v>
       </c>
@@ -2703,19 +2697,19 @@
       <c r="J44" s="4">
         <v>25296</v>
       </c>
-      <c r="K44" s="12"/>
-      <c r="L44" s="16">
+      <c r="K44" s="4"/>
+      <c r="L44" s="13">
         <f t="shared" si="0"/>
         <v>-5.63694267515924E-2</v>
       </c>
-      <c r="M44" s="16">
+      <c r="M44" s="13">
         <f t="shared" si="1"/>
         <v>8.650487221915748E-3</v>
       </c>
-      <c r="N44" s="12"/>
-      <c r="O44" s="12"/>
-      <c r="P44" s="12"/>
-      <c r="Q44" s="12"/>
+      <c r="N44" s="4"/>
+      <c r="O44" s="4"/>
+      <c r="P44" s="4"/>
+      <c r="Q44" s="4"/>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="3" t="s">
@@ -2733,7 +2727,7 @@
       <c r="E45" s="4">
         <v>33195</v>
       </c>
-      <c r="F45" s="12"/>
+      <c r="F45" s="4"/>
       <c r="G45" s="4">
         <v>2548</v>
       </c>
@@ -2746,19 +2740,19 @@
       <c r="J45" s="4">
         <v>25813</v>
       </c>
-      <c r="K45" s="12"/>
-      <c r="L45" s="17">
+      <c r="K45" s="4"/>
+      <c r="L45" s="14">
         <f t="shared" si="0"/>
         <v>7.4654696132596676E-2</v>
       </c>
-      <c r="M45" s="16">
+      <c r="M45" s="13">
         <f t="shared" si="1"/>
         <v>-1.8669980418737797E-2</v>
       </c>
-      <c r="N45" s="12"/>
-      <c r="O45" s="12"/>
-      <c r="P45" s="12"/>
-      <c r="Q45" s="12"/>
+      <c r="N45" s="4"/>
+      <c r="O45" s="4"/>
+      <c r="P45" s="4"/>
+      <c r="Q45" s="4"/>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="3" t="s">
@@ -2776,7 +2770,7 @@
       <c r="E46" s="4">
         <v>45055</v>
       </c>
-      <c r="F46" s="12"/>
+      <c r="F46" s="4"/>
       <c r="G46" s="4">
         <v>1348</v>
       </c>
@@ -2789,19 +2783,19 @@
       <c r="J46" s="4">
         <v>25813</v>
       </c>
-      <c r="K46" s="12"/>
-      <c r="L46" s="16">
+      <c r="K46" s="4"/>
+      <c r="L46" s="13">
         <f t="shared" si="0"/>
         <v>-6.062500000000004E-2</v>
       </c>
-      <c r="M46" s="16">
+      <c r="M46" s="13">
         <f t="shared" si="1"/>
         <v>8.2177338808122613E-3</v>
       </c>
-      <c r="N46" s="12"/>
-      <c r="O46" s="12"/>
-      <c r="P46" s="12"/>
-      <c r="Q46" s="12"/>
+      <c r="N46" s="4"/>
+      <c r="O46" s="4"/>
+      <c r="P46" s="4"/>
+      <c r="Q46" s="4"/>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="3" t="s">
@@ -2819,7 +2813,7 @@
       <c r="E47" s="4">
         <v>47515</v>
       </c>
-      <c r="F47" s="12"/>
+      <c r="F47" s="4"/>
       <c r="G47" s="4">
         <v>4118</v>
       </c>
@@ -2832,19 +2826,19 @@
       <c r="J47" s="4">
         <v>26623</v>
       </c>
-      <c r="K47" s="12"/>
-      <c r="L47" s="16">
+      <c r="K47" s="4"/>
+      <c r="L47" s="13">
         <f t="shared" si="0"/>
         <v>-1.5630114566284714E-2</v>
       </c>
-      <c r="M47" s="16">
+      <c r="M47" s="13">
         <f t="shared" si="1"/>
         <v>3.4778491002840362E-3</v>
       </c>
-      <c r="N47" s="12"/>
-      <c r="O47" s="12"/>
-      <c r="P47" s="12"/>
-      <c r="Q47" s="12"/>
+      <c r="N47" s="4"/>
+      <c r="O47" s="4"/>
+      <c r="P47" s="4"/>
+      <c r="Q47" s="4"/>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="3" t="s">
@@ -2862,7 +2856,7 @@
       <c r="E48" s="4">
         <v>38197</v>
       </c>
-      <c r="F48" s="12"/>
+      <c r="F48" s="4"/>
       <c r="G48" s="4">
         <v>10021</v>
       </c>
@@ -2875,19 +2869,19 @@
       <c r="J48" s="4">
         <v>21597</v>
       </c>
-      <c r="K48" s="12"/>
-      <c r="L48" s="16">
+      <c r="K48" s="4"/>
+      <c r="L48" s="13">
         <f t="shared" si="0"/>
         <v>2.1579118028534294E-2</v>
       </c>
-      <c r="M48" s="16">
+      <c r="M48" s="13">
         <f t="shared" si="1"/>
         <v>6.6798439668036558E-3</v>
       </c>
-      <c r="N48" s="12"/>
-      <c r="O48" s="12"/>
-      <c r="P48" s="12"/>
-      <c r="Q48" s="12"/>
+      <c r="N48" s="4"/>
+      <c r="O48" s="4"/>
+      <c r="P48" s="4"/>
+      <c r="Q48" s="4"/>
     </row>
     <row r="49" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="3" t="s">
@@ -2905,7 +2899,7 @@
       <c r="E49" s="4">
         <v>44215</v>
       </c>
-      <c r="F49" s="12"/>
+      <c r="F49" s="4"/>
       <c r="G49" s="4">
         <v>2684</v>
       </c>
@@ -2918,19 +2912,19 @@
       <c r="J49" s="4">
         <v>29992</v>
       </c>
-      <c r="K49" s="12"/>
-      <c r="L49" s="16">
+      <c r="K49" s="4"/>
+      <c r="L49" s="13">
         <f t="shared" si="0"/>
         <v>7.3681125439624795E-2</v>
       </c>
-      <c r="M49" s="16">
+      <c r="M49" s="13">
         <f t="shared" si="1"/>
         <v>3.2228881601259474E-4</v>
       </c>
-      <c r="N49" s="12"/>
-      <c r="O49" s="12"/>
-      <c r="P49" s="12"/>
-      <c r="Q49" s="12"/>
+      <c r="N49" s="4"/>
+      <c r="O49" s="4"/>
+      <c r="P49" s="4"/>
+      <c r="Q49" s="4"/>
     </row>
     <row r="50" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="3" t="s">
@@ -2948,7 +2942,7 @@
       <c r="E50" s="4">
         <v>4885</v>
       </c>
-      <c r="F50" s="12"/>
+      <c r="F50" s="4"/>
       <c r="G50" s="4">
         <v>922</v>
       </c>
@@ -2961,19 +2955,19 @@
       <c r="J50" s="4">
         <v>3415</v>
       </c>
-      <c r="K50" s="12"/>
-      <c r="L50" s="16">
+      <c r="K50" s="4"/>
+      <c r="L50" s="13">
         <f t="shared" si="0"/>
         <v>-2.934782608695663E-2</v>
       </c>
-      <c r="M50" s="16">
+      <c r="M50" s="13">
         <f t="shared" si="1"/>
         <v>-2.4411463664278488E-2</v>
       </c>
-      <c r="N50" s="12"/>
-      <c r="O50" s="12"/>
-      <c r="P50" s="12"/>
-      <c r="Q50" s="12"/>
+      <c r="N50" s="4"/>
+      <c r="O50" s="4"/>
+      <c r="P50" s="4"/>
+      <c r="Q50" s="4"/>
     </row>
     <row r="51" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="3" t="s">
@@ -2991,7 +2985,7 @@
       <c r="E51" s="4">
         <v>20077</v>
       </c>
-      <c r="F51" s="12"/>
+      <c r="F51" s="4"/>
       <c r="G51" s="4">
         <v>2281</v>
       </c>
@@ -3004,19 +2998,19 @@
       <c r="J51" s="4">
         <v>15711</v>
       </c>
-      <c r="K51" s="12"/>
-      <c r="L51" s="16">
+      <c r="K51" s="4"/>
+      <c r="L51" s="13">
         <f t="shared" si="0"/>
         <v>2.7137546468401386E-2</v>
       </c>
-      <c r="M51" s="16">
+      <c r="M51" s="13">
         <f t="shared" si="1"/>
         <v>7.5459480998163464E-4</v>
       </c>
-      <c r="N51" s="12"/>
-      <c r="O51" s="12"/>
-      <c r="P51" s="12"/>
-      <c r="Q51" s="12"/>
+      <c r="N51" s="4"/>
+      <c r="O51" s="4"/>
+      <c r="P51" s="4"/>
+      <c r="Q51" s="4"/>
     </row>
     <row r="52" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="5" t="s">
@@ -3034,7 +3028,7 @@
       <c r="E52" s="6">
         <v>1779631</v>
       </c>
-      <c r="F52" s="13"/>
+      <c r="F52" s="12"/>
       <c r="G52" s="6">
         <v>156766</v>
       </c>
@@ -3047,19 +3041,19 @@
       <c r="J52" s="6">
         <v>1162974</v>
       </c>
-      <c r="K52" s="13"/>
-      <c r="L52" s="16">
+      <c r="K52" s="12"/>
+      <c r="L52" s="13">
         <f t="shared" si="0"/>
         <v>4.0468961555820027E-2</v>
       </c>
-      <c r="M52" s="16">
+      <c r="M52" s="13">
         <f t="shared" si="1"/>
         <v>-1.0100689412579911E-3</v>
       </c>
-      <c r="N52" s="13"/>
-      <c r="O52" s="13"/>
-      <c r="P52" s="13"/>
-      <c r="Q52" s="13"/>
+      <c r="N52" s="12"/>
+      <c r="O52" s="12"/>
+      <c r="P52" s="12"/>
+      <c r="Q52" s="12"/>
       <c r="S52" s="10">
         <f>SUM(B2:B51)</f>
         <v>186046</v>
@@ -3142,7 +3136,7 @@
       <c r="E53" s="4">
         <v>16606</v>
       </c>
-      <c r="F53" s="12"/>
+      <c r="F53" s="4"/>
       <c r="G53" s="4">
         <v>7393</v>
       </c>
@@ -3155,19 +3149,19 @@
       <c r="J53" s="4">
         <v>9598</v>
       </c>
-      <c r="K53" s="12"/>
-      <c r="L53" s="16">
+      <c r="K53" s="4"/>
+      <c r="L53" s="13">
         <f t="shared" si="0"/>
         <v>4.8039440495297736E-3</v>
       </c>
-      <c r="M53" s="16">
+      <c r="M53" s="13">
         <f t="shared" si="1"/>
         <v>-7.0034927134769998E-3</v>
       </c>
-      <c r="N53" s="12"/>
-      <c r="O53" s="12"/>
-      <c r="P53" s="12"/>
-      <c r="Q53" s="12"/>
+      <c r="N53" s="4"/>
+      <c r="O53" s="4"/>
+      <c r="P53" s="4"/>
+      <c r="Q53" s="4"/>
     </row>
     <row r="54" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="3" t="s">
@@ -3185,7 +3179,7 @@
       <c r="E54" s="4">
         <v>12426</v>
       </c>
-      <c r="F54" s="12"/>
+      <c r="F54" s="4"/>
       <c r="G54" s="4">
         <v>1267</v>
       </c>
@@ -3198,19 +3192,19 @@
       <c r="J54" s="4">
         <v>8000</v>
       </c>
-      <c r="K54" s="12"/>
-      <c r="L54" s="17">
+      <c r="K54" s="4"/>
+      <c r="L54" s="14">
         <f t="shared" si="0"/>
         <v>0.13593314763231201</v>
       </c>
-      <c r="M54" s="16">
+      <c r="M54" s="13">
         <f t="shared" si="1"/>
         <v>-6.7785288910349295E-2</v>
       </c>
-      <c r="N54" s="12"/>
-      <c r="O54" s="12"/>
-      <c r="P54" s="12"/>
-      <c r="Q54" s="12"/>
+      <c r="N54" s="4"/>
+      <c r="O54" s="4"/>
+      <c r="P54" s="4"/>
+      <c r="Q54" s="4"/>
     </row>
     <row r="55" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="3" t="s">
@@ -3228,7 +3222,7 @@
       <c r="E55" s="4">
         <v>12358</v>
       </c>
-      <c r="F55" s="12"/>
+      <c r="F55" s="4"/>
       <c r="G55" s="4">
         <v>408</v>
       </c>
@@ -3241,19 +3235,19 @@
       <c r="J55" s="4">
         <v>7436</v>
       </c>
-      <c r="K55" s="12"/>
-      <c r="L55" s="16">
+      <c r="K55" s="4"/>
+      <c r="L55" s="13">
         <f t="shared" si="0"/>
         <v>-0.15206718346253234</v>
       </c>
-      <c r="M55" s="16">
+      <c r="M55" s="13">
         <f t="shared" si="1"/>
         <v>-4.0613367858876925E-2</v>
       </c>
-      <c r="N55" s="12"/>
-      <c r="O55" s="12"/>
-      <c r="P55" s="12"/>
-      <c r="Q55" s="12"/>
+      <c r="N55" s="4"/>
+      <c r="O55" s="4"/>
+      <c r="P55" s="4"/>
+      <c r="Q55" s="4"/>
     </row>
     <row r="56" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="3" t="s">
@@ -3271,7 +3265,7 @@
       <c r="E56" s="4">
         <v>9347</v>
       </c>
-      <c r="F56" s="12"/>
+      <c r="F56" s="4"/>
       <c r="G56" s="4">
         <v>762</v>
       </c>
@@ -3284,19 +3278,19 @@
       <c r="J56" s="4">
         <v>6650</v>
       </c>
-      <c r="K56" s="12"/>
-      <c r="L56" s="16">
+      <c r="K56" s="4"/>
+      <c r="L56" s="13">
         <f t="shared" si="0"/>
         <v>-1.8033356497567876E-2</v>
       </c>
-      <c r="M56" s="16">
+      <c r="M56" s="13">
         <f t="shared" si="1"/>
         <v>-4.5399593452444709E-2</v>
       </c>
-      <c r="N56" s="12"/>
-      <c r="O56" s="12"/>
-      <c r="P56" s="12"/>
-      <c r="Q56" s="12"/>
+      <c r="N56" s="4"/>
+      <c r="O56" s="4"/>
+      <c r="P56" s="4"/>
+      <c r="Q56" s="4"/>
     </row>
     <row r="57" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="3" t="s">
@@ -3314,7 +3308,7 @@
       <c r="E57" s="4">
         <v>17190</v>
       </c>
-      <c r="F57" s="12"/>
+      <c r="F57" s="4"/>
       <c r="G57" s="4">
         <v>915</v>
       </c>
@@ -3327,19 +3321,19 @@
       <c r="J57" s="4">
         <v>10445</v>
       </c>
-      <c r="K57" s="12"/>
-      <c r="L57" s="17">
+      <c r="K57" s="4"/>
+      <c r="L57" s="14">
         <f t="shared" si="0"/>
         <v>0.18529411764705883</v>
       </c>
-      <c r="M57" s="16">
+      <c r="M57" s="13">
         <f t="shared" si="1"/>
         <v>-5.8318789994182718E-2</v>
       </c>
-      <c r="N57" s="12"/>
-      <c r="O57" s="12"/>
-      <c r="P57" s="12"/>
-      <c r="Q57" s="12"/>
+      <c r="N57" s="4"/>
+      <c r="O57" s="4"/>
+      <c r="P57" s="4"/>
+      <c r="Q57" s="4"/>
     </row>
     <row r="58" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="3" t="s">
@@ -3357,7 +3351,7 @@
       <c r="E58" s="4">
         <v>13694</v>
       </c>
-      <c r="F58" s="12"/>
+      <c r="F58" s="4"/>
       <c r="G58" s="4">
         <v>2129</v>
       </c>
@@ -3370,19 +3364,19 @@
       <c r="J58" s="4">
         <v>8091</v>
       </c>
-      <c r="K58" s="12"/>
-      <c r="L58" s="16">
+      <c r="K58" s="4"/>
+      <c r="L58" s="13">
         <f t="shared" si="0"/>
         <v>3.4091622215249417E-2</v>
       </c>
-      <c r="M58" s="16">
+      <c r="M58" s="13">
         <f t="shared" si="1"/>
         <v>-5.0511172776398494E-2</v>
       </c>
-      <c r="N58" s="12"/>
-      <c r="O58" s="12"/>
-      <c r="P58" s="12"/>
-      <c r="Q58" s="12"/>
+      <c r="N58" s="4"/>
+      <c r="O58" s="4"/>
+      <c r="P58" s="4"/>
+      <c r="Q58" s="4"/>
     </row>
     <row r="59" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="3" t="s">
@@ -3400,7 +3394,7 @@
       <c r="E59" s="4">
         <v>9920</v>
       </c>
-      <c r="F59" s="12"/>
+      <c r="F59" s="4"/>
       <c r="G59" s="4">
         <v>1224</v>
       </c>
@@ -3413,19 +3407,19 @@
       <c r="J59" s="4">
         <v>6287</v>
       </c>
-      <c r="K59" s="12"/>
-      <c r="L59" s="16">
+      <c r="K59" s="4"/>
+      <c r="L59" s="13">
         <f t="shared" si="0"/>
         <v>2.2455089820359264E-2</v>
       </c>
-      <c r="M59" s="16">
+      <c r="M59" s="13">
         <f t="shared" si="1"/>
         <v>-4.1229838709677447E-2</v>
       </c>
-      <c r="N59" s="12"/>
-      <c r="O59" s="12"/>
-      <c r="P59" s="12"/>
-      <c r="Q59" s="12"/>
+      <c r="N59" s="4"/>
+      <c r="O59" s="4"/>
+      <c r="P59" s="4"/>
+      <c r="Q59" s="4"/>
     </row>
     <row r="60" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="3" t="s">
@@ -3443,7 +3437,7 @@
       <c r="E60" s="4">
         <v>11673</v>
       </c>
-      <c r="F60" s="12"/>
+      <c r="F60" s="4"/>
       <c r="G60" s="4">
         <v>1214</v>
       </c>
@@ -3456,19 +3450,19 @@
       <c r="J60" s="4">
         <v>6859</v>
       </c>
-      <c r="K60" s="12"/>
-      <c r="L60" s="17">
+      <c r="K60" s="4"/>
+      <c r="L60" s="14">
         <f t="shared" si="0"/>
         <v>7.7027027027027017E-2</v>
       </c>
-      <c r="M60" s="16">
+      <c r="M60" s="13">
         <f t="shared" si="1"/>
         <v>-4.4774265398783486E-2</v>
       </c>
-      <c r="N60" s="12"/>
-      <c r="O60" s="12"/>
-      <c r="P60" s="12"/>
-      <c r="Q60" s="12"/>
+      <c r="N60" s="4"/>
+      <c r="O60" s="4"/>
+      <c r="P60" s="4"/>
+      <c r="Q60" s="4"/>
     </row>
     <row r="61" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="3" t="s">
@@ -3486,7 +3480,7 @@
       <c r="E61" s="4">
         <v>8693</v>
       </c>
-      <c r="F61" s="12"/>
+      <c r="F61" s="4"/>
       <c r="G61" s="4">
         <v>555</v>
       </c>
@@ -3499,19 +3493,19 @@
       <c r="J61" s="4">
         <v>5845</v>
       </c>
-      <c r="K61" s="12"/>
-      <c r="L61" s="16">
+      <c r="K61" s="4"/>
+      <c r="L61" s="13">
         <f t="shared" si="0"/>
         <v>4.4855305466237949E-2</v>
       </c>
-      <c r="M61" s="16">
+      <c r="M61" s="13">
         <f t="shared" si="1"/>
         <v>-8.0121937190844594E-3</v>
       </c>
-      <c r="N61" s="12"/>
-      <c r="O61" s="12"/>
-      <c r="P61" s="12"/>
-      <c r="Q61" s="12"/>
+      <c r="N61" s="4"/>
+      <c r="O61" s="4"/>
+      <c r="P61" s="4"/>
+      <c r="Q61" s="4"/>
     </row>
     <row r="62" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="3" t="s">
@@ -3529,7 +3523,7 @@
       <c r="E62" s="4">
         <v>12308</v>
       </c>
-      <c r="F62" s="12"/>
+      <c r="F62" s="4"/>
       <c r="G62" s="4">
         <v>164</v>
       </c>
@@ -3542,19 +3536,19 @@
       <c r="J62" s="4">
         <v>8042</v>
       </c>
-      <c r="K62" s="12"/>
-      <c r="L62" s="17">
+      <c r="K62" s="4"/>
+      <c r="L62" s="14">
         <f t="shared" si="0"/>
         <v>0.26219512195121952</v>
       </c>
-      <c r="M62" s="16">
+      <c r="M62" s="13">
         <f t="shared" si="1"/>
         <v>-0.11491712707182322</v>
       </c>
-      <c r="N62" s="12"/>
-      <c r="O62" s="12"/>
-      <c r="P62" s="12"/>
-      <c r="Q62" s="12"/>
+      <c r="N62" s="4"/>
+      <c r="O62" s="4"/>
+      <c r="P62" s="4"/>
+      <c r="Q62" s="4"/>
     </row>
     <row r="63" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="5" t="s">
@@ -3572,7 +3566,7 @@
       <c r="E63" s="6">
         <v>124216</v>
       </c>
-      <c r="F63" s="13"/>
+      <c r="F63" s="12"/>
       <c r="G63" s="6">
         <v>16031</v>
       </c>
@@ -3585,19 +3579,19 @@
       <c r="J63" s="6">
         <v>77253</v>
       </c>
-      <c r="K63" s="13"/>
-      <c r="L63" s="16">
+      <c r="K63" s="12"/>
+      <c r="L63" s="13">
         <f t="shared" si="0"/>
         <v>3.1818181818181746E-2</v>
       </c>
-      <c r="M63" s="16">
+      <c r="M63" s="13">
         <f t="shared" si="1"/>
         <v>-4.8269144071617198E-2</v>
       </c>
-      <c r="N63" s="13"/>
-      <c r="O63" s="13"/>
-      <c r="P63" s="13"/>
-      <c r="Q63" s="13"/>
+      <c r="N63" s="12"/>
+      <c r="O63" s="12"/>
+      <c r="P63" s="12"/>
+      <c r="Q63" s="12"/>
       <c r="S63" s="10">
         <f>SUM(B53:B62)</f>
         <v>22729</v>
@@ -3679,7 +3673,7 @@
       <c r="E64" s="6">
         <v>1903847</v>
       </c>
-      <c r="F64" s="13"/>
+      <c r="F64" s="12"/>
       <c r="G64" s="6">
         <v>172797</v>
       </c>
@@ -3692,49 +3686,49 @@
       <c r="J64" s="6">
         <v>1240227</v>
       </c>
-      <c r="K64" s="13"/>
-      <c r="L64" s="16">
+      <c r="K64" s="12"/>
+      <c r="L64" s="13">
         <f t="shared" si="0"/>
         <v>3.9520459657344409E-2</v>
       </c>
-      <c r="M64" s="16">
+      <c r="M64" s="13">
         <f t="shared" si="1"/>
         <v>-4.0934749483545474E-3</v>
       </c>
-      <c r="N64" s="13"/>
-      <c r="O64" s="13"/>
-      <c r="P64" s="13"/>
-      <c r="Q64" s="13"/>
+      <c r="N64" s="12"/>
+      <c r="O64" s="12"/>
+      <c r="P64" s="12"/>
+      <c r="Q64" s="12"/>
       <c r="S64" s="10">
-        <f>SUM(S52:S63)</f>
+        <f t="shared" ref="S64:Z64" si="8">SUM(S52:S63)</f>
         <v>208775</v>
       </c>
       <c r="T64" s="10">
-        <f>SUM(T52:T63)</f>
+        <f t="shared" si="8"/>
         <v>191627</v>
       </c>
       <c r="U64" s="10">
-        <f>SUM(U52:U63)</f>
+        <f t="shared" si="8"/>
         <v>1991246</v>
       </c>
       <c r="V64" s="10">
-        <f>SUM(V52:V63)</f>
+        <f t="shared" si="8"/>
         <v>1903890</v>
       </c>
       <c r="W64" s="10">
-        <f>SUM(W52:W63)</f>
+        <f t="shared" si="8"/>
         <v>172797</v>
       </c>
       <c r="X64" s="10">
-        <f>SUM(X52:X63)</f>
+        <f t="shared" si="8"/>
         <v>146332</v>
       </c>
       <c r="Y64" s="10">
-        <f>SUM(Y52:Y63)</f>
+        <f t="shared" si="8"/>
         <v>1299901</v>
       </c>
       <c r="Z64" s="10">
-        <f>SUM(Z52:Z63)</f>
+        <f t="shared" si="8"/>
         <v>1240387</v>
       </c>
       <c r="AB64" s="10">
@@ -3786,7 +3780,7 @@
       <c r="E65" s="4">
         <v>5336</v>
       </c>
-      <c r="F65" s="12"/>
+      <c r="F65" s="4"/>
       <c r="G65" s="4">
         <v>683</v>
       </c>
@@ -3799,19 +3793,19 @@
       <c r="J65" s="4">
         <v>3939</v>
       </c>
-      <c r="K65" s="12"/>
-      <c r="L65" s="16">
+      <c r="K65" s="4"/>
+      <c r="L65" s="13">
         <f t="shared" si="0"/>
         <v>4.2850510677808762E-2</v>
       </c>
-      <c r="M65" s="17">
+      <c r="M65" s="14">
         <f t="shared" si="1"/>
         <v>0.16158170914542724</v>
       </c>
-      <c r="N65" s="12"/>
-      <c r="O65" s="12"/>
-      <c r="P65" s="12"/>
-      <c r="Q65" s="12"/>
+      <c r="N65" s="4"/>
+      <c r="O65" s="4"/>
+      <c r="P65" s="4"/>
+      <c r="Q65" s="4"/>
     </row>
     <row r="66" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="3" t="s">
@@ -3829,7 +3823,7 @@
       <c r="E66" s="4">
         <v>6821</v>
       </c>
-      <c r="F66" s="12"/>
+      <c r="F66" s="4"/>
       <c r="G66" s="4">
         <v>264</v>
       </c>
@@ -3842,19 +3836,19 @@
       <c r="J66" s="4">
         <v>5570</v>
       </c>
-      <c r="K66" s="12"/>
-      <c r="L66" s="16">
+      <c r="K66" s="4"/>
+      <c r="L66" s="13">
         <f t="shared" si="0"/>
         <v>-1.1538461538461497E-2</v>
       </c>
-      <c r="M66" s="16">
+      <c r="M66" s="13">
         <f t="shared" si="1"/>
         <v>5.8195279284562362E-2</v>
       </c>
-      <c r="N66" s="12"/>
-      <c r="O66" s="12"/>
-      <c r="P66" s="12"/>
-      <c r="Q66" s="12"/>
+      <c r="N66" s="4"/>
+      <c r="O66" s="4"/>
+      <c r="P66" s="4"/>
+      <c r="Q66" s="4"/>
     </row>
     <row r="67" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="3" t="s">
@@ -3872,7 +3866,7 @@
       <c r="E67" s="4">
         <v>6363</v>
       </c>
-      <c r="F67" s="12"/>
+      <c r="F67" s="4"/>
       <c r="G67" s="4">
         <v>1055</v>
       </c>
@@ -3885,19 +3879,19 @@
       <c r="J67" s="4">
         <v>3950</v>
       </c>
-      <c r="K67" s="12"/>
-      <c r="L67" s="16">
+      <c r="K67" s="4"/>
+      <c r="L67" s="13">
         <f>B67/C67-1.05</f>
         <v>3.072372999304096E-2</v>
       </c>
-      <c r="M67" s="17">
+      <c r="M67" s="14">
         <f>D67/E67-1.05</f>
         <v>0.10417256011315423</v>
       </c>
-      <c r="N67" s="12"/>
-      <c r="O67" s="12"/>
-      <c r="P67" s="12"/>
-      <c r="Q67" s="12"/>
+      <c r="N67" s="4"/>
+      <c r="O67" s="4"/>
+      <c r="P67" s="4"/>
+      <c r="Q67" s="4"/>
     </row>
     <row r="68" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="3" t="s">
@@ -3915,7 +3909,7 @@
       <c r="E68" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="F68" s="14"/>
+      <c r="F68" s="9"/>
       <c r="G68" s="9" t="s">
         <v>76</v>
       </c>
@@ -3928,13 +3922,13 @@
       <c r="J68" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="K68" s="14"/>
-      <c r="L68" s="16"/>
-      <c r="M68" s="16"/>
-      <c r="N68" s="14"/>
-      <c r="O68" s="14"/>
-      <c r="P68" s="14"/>
-      <c r="Q68" s="14"/>
+      <c r="K68" s="9"/>
+      <c r="L68" s="13"/>
+      <c r="M68" s="13"/>
+      <c r="N68" s="9"/>
+      <c r="O68" s="9"/>
+      <c r="P68" s="9"/>
+      <c r="Q68" s="9"/>
     </row>
     <row r="69" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="3" t="s">
@@ -3952,7 +3946,7 @@
       <c r="E69" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="F69" s="14"/>
+      <c r="F69" s="9"/>
       <c r="G69" s="9" t="s">
         <v>76</v>
       </c>
@@ -3965,13 +3959,13 @@
       <c r="J69" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="K69" s="14"/>
-      <c r="L69" s="16"/>
-      <c r="M69" s="16"/>
-      <c r="N69" s="14"/>
-      <c r="O69" s="14"/>
-      <c r="P69" s="14"/>
-      <c r="Q69" s="14"/>
+      <c r="K69" s="9"/>
+      <c r="L69" s="13"/>
+      <c r="M69" s="13"/>
+      <c r="N69" s="9"/>
+      <c r="O69" s="9"/>
+      <c r="P69" s="9"/>
+      <c r="Q69" s="9"/>
     </row>
     <row r="70" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="3" t="s">
@@ -3989,7 +3983,7 @@
       <c r="E70" s="4">
         <v>30982</v>
       </c>
-      <c r="F70" s="12"/>
+      <c r="F70" s="4"/>
       <c r="G70" s="4">
         <v>2184</v>
       </c>
@@ -4002,19 +3996,19 @@
       <c r="J70" s="4">
         <v>19139</v>
       </c>
-      <c r="K70" s="12"/>
-      <c r="L70" s="16">
-        <f>B70/C70-1.05</f>
+      <c r="K70" s="4"/>
+      <c r="L70" s="13">
+        <f t="shared" ref="L70:L77" si="9">B70/C70-1.05</f>
         <v>-6.0214504596527108E-2</v>
       </c>
-      <c r="M70" s="16">
-        <f>D70/E70-1.05</f>
+      <c r="M70" s="13">
+        <f t="shared" ref="M70:M77" si="10">D70/E70-1.05</f>
         <v>4.3473629849590134E-2</v>
       </c>
-      <c r="N70" s="12"/>
-      <c r="O70" s="12"/>
-      <c r="P70" s="12"/>
-      <c r="Q70" s="12"/>
+      <c r="N70" s="4"/>
+      <c r="O70" s="4"/>
+      <c r="P70" s="4"/>
+      <c r="Q70" s="4"/>
     </row>
     <row r="71" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="3" t="s">
@@ -4032,7 +4026,7 @@
       <c r="E71" s="4">
         <v>10693</v>
       </c>
-      <c r="F71" s="12"/>
+      <c r="F71" s="4"/>
       <c r="G71" s="4">
         <v>175</v>
       </c>
@@ -4045,19 +4039,19 @@
       <c r="J71" s="4">
         <v>4878</v>
       </c>
-      <c r="K71" s="12"/>
-      <c r="L71" s="17">
-        <f>B71/C71-1.05</f>
+      <c r="K71" s="4"/>
+      <c r="L71" s="14">
+        <f t="shared" si="9"/>
         <v>0.17256097560975614</v>
       </c>
-      <c r="M71" s="17">
-        <f>D71/E71-1.05</f>
+      <c r="M71" s="14">
+        <f t="shared" si="10"/>
         <v>8.2236042270644294E-2</v>
       </c>
-      <c r="N71" s="12"/>
-      <c r="O71" s="12"/>
-      <c r="P71" s="12"/>
-      <c r="Q71" s="12"/>
+      <c r="N71" s="4"/>
+      <c r="O71" s="4"/>
+      <c r="P71" s="4"/>
+      <c r="Q71" s="4"/>
     </row>
     <row r="72" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="3" t="s">
@@ -4075,7 +4069,7 @@
       <c r="E72" s="4">
         <v>22118</v>
       </c>
-      <c r="F72" s="12"/>
+      <c r="F72" s="4"/>
       <c r="G72" s="4">
         <v>576</v>
       </c>
@@ -4088,19 +4082,19 @@
       <c r="J72" s="4">
         <v>12144</v>
       </c>
-      <c r="K72" s="12"/>
-      <c r="L72" s="16">
-        <f>B72/C72-1.05</f>
+      <c r="K72" s="4"/>
+      <c r="L72" s="13">
+        <f t="shared" si="9"/>
         <v>1.2572421784472709E-2</v>
       </c>
-      <c r="M72" s="16">
-        <f>D72/E72-1.05</f>
+      <c r="M72" s="13">
+        <f t="shared" si="10"/>
         <v>-1.6407450944931679E-2</v>
       </c>
-      <c r="N72" s="12"/>
-      <c r="O72" s="12"/>
-      <c r="P72" s="12"/>
-      <c r="Q72" s="12"/>
+      <c r="N72" s="4"/>
+      <c r="O72" s="4"/>
+      <c r="P72" s="4"/>
+      <c r="Q72" s="4"/>
     </row>
     <row r="73" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="3" t="s">
@@ -4118,7 +4112,7 @@
       <c r="E73" s="4">
         <v>9996</v>
       </c>
-      <c r="F73" s="12"/>
+      <c r="F73" s="4"/>
       <c r="G73" s="4">
         <v>1339</v>
       </c>
@@ -4131,19 +4125,19 @@
       <c r="J73" s="4">
         <v>5636</v>
       </c>
-      <c r="K73" s="12"/>
-      <c r="L73" s="16">
-        <f>B73/C73-1.05</f>
+      <c r="K73" s="4"/>
+      <c r="L73" s="13">
+        <f t="shared" si="9"/>
         <v>4.3226022803487529E-2</v>
       </c>
-      <c r="M73" s="16">
-        <f>D73/E73-1.05</f>
+      <c r="M73" s="13">
+        <f t="shared" si="10"/>
         <v>9.1236494597839446E-3</v>
       </c>
-      <c r="N73" s="12"/>
-      <c r="O73" s="12"/>
-      <c r="P73" s="12"/>
-      <c r="Q73" s="12"/>
+      <c r="N73" s="4"/>
+      <c r="O73" s="4"/>
+      <c r="P73" s="4"/>
+      <c r="Q73" s="4"/>
     </row>
     <row r="74" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="3" t="s">
@@ -4161,7 +4155,7 @@
       <c r="E74" s="4">
         <v>10623</v>
       </c>
-      <c r="F74" s="12"/>
+      <c r="F74" s="4"/>
       <c r="G74" s="4">
         <v>1851</v>
       </c>
@@ -4174,19 +4168,19 @@
       <c r="J74" s="4">
         <v>7190</v>
       </c>
-      <c r="K74" s="12"/>
-      <c r="L74" s="17">
-        <f>B74/C74-1.05</f>
+      <c r="K74" s="4"/>
+      <c r="L74" s="14">
+        <f t="shared" si="9"/>
         <v>0.11434406535319552</v>
       </c>
-      <c r="M74" s="17">
-        <f>D74/E74-1.05</f>
+      <c r="M74" s="14">
+        <f t="shared" si="10"/>
         <v>0.18420879224324582</v>
       </c>
-      <c r="N74" s="12"/>
-      <c r="O74" s="12"/>
-      <c r="P74" s="12"/>
-      <c r="Q74" s="12"/>
+      <c r="N74" s="4"/>
+      <c r="O74" s="4"/>
+      <c r="P74" s="4"/>
+      <c r="Q74" s="4"/>
     </row>
     <row r="75" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="3" t="s">
@@ -4204,7 +4198,7 @@
       <c r="E75" s="4">
         <v>175</v>
       </c>
-      <c r="F75" s="12"/>
+      <c r="F75" s="4"/>
       <c r="G75" s="4">
         <v>57</v>
       </c>
@@ -4217,19 +4211,19 @@
       <c r="J75" s="4">
         <v>92</v>
       </c>
-      <c r="K75" s="12"/>
-      <c r="L75" s="17">
-        <f>B75/C75-1.05</f>
+      <c r="K75" s="4"/>
+      <c r="L75" s="14">
+        <f t="shared" si="9"/>
         <v>0.36538461538461542</v>
       </c>
-      <c r="M75" s="17">
-        <f>D75/E75-1.05</f>
+      <c r="M75" s="14">
+        <f t="shared" si="10"/>
         <v>0.14428571428571435</v>
       </c>
-      <c r="N75" s="12"/>
-      <c r="O75" s="12"/>
-      <c r="P75" s="12"/>
-      <c r="Q75" s="12"/>
+      <c r="N75" s="4"/>
+      <c r="O75" s="4"/>
+      <c r="P75" s="4"/>
+      <c r="Q75" s="4"/>
     </row>
     <row r="76" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="3" t="s">
@@ -4247,7 +4241,7 @@
       <c r="E76" s="4">
         <v>8980</v>
       </c>
-      <c r="F76" s="12"/>
+      <c r="F76" s="4"/>
       <c r="G76" s="4">
         <v>608</v>
       </c>
@@ -4260,19 +4254,19 @@
       <c r="J76" s="4">
         <v>4846</v>
       </c>
-      <c r="K76" s="12"/>
-      <c r="L76" s="17">
-        <f>B76/C76-1.05</f>
+      <c r="K76" s="4"/>
+      <c r="L76" s="14">
+        <f t="shared" si="9"/>
         <v>0.17280887011615631</v>
       </c>
-      <c r="M76" s="17">
-        <f>D76/E76-1.05</f>
+      <c r="M76" s="14">
+        <f t="shared" si="10"/>
         <v>0.12371937639198216</v>
       </c>
-      <c r="N76" s="12"/>
-      <c r="O76" s="12"/>
-      <c r="P76" s="12"/>
-      <c r="Q76" s="12"/>
+      <c r="N76" s="4"/>
+      <c r="O76" s="4"/>
+      <c r="P76" s="4"/>
+      <c r="Q76" s="4"/>
     </row>
     <row r="77" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="5" t="s">
@@ -4290,7 +4284,7 @@
       <c r="E77" s="6">
         <v>112087</v>
       </c>
-      <c r="F77" s="13"/>
+      <c r="F77" s="12"/>
       <c r="G77" s="6">
         <v>8792</v>
       </c>
@@ -4303,19 +4297,19 @@
       <c r="J77" s="6">
         <v>67384</v>
       </c>
-      <c r="K77" s="13"/>
-      <c r="L77" s="16">
-        <f>B77/C77-1.05</f>
+      <c r="K77" s="12"/>
+      <c r="L77" s="13">
+        <f t="shared" si="9"/>
         <v>4.0134297520661111E-2</v>
       </c>
-      <c r="M77" s="16">
-        <f>D77/E77-1.05</f>
+      <c r="M77" s="13">
+        <f t="shared" si="10"/>
         <v>6.2180716764655974E-2</v>
       </c>
-      <c r="N77" s="13"/>
-      <c r="O77" s="13"/>
-      <c r="P77" s="13"/>
-      <c r="Q77" s="13"/>
+      <c r="N77" s="12"/>
+      <c r="O77" s="12"/>
+      <c r="P77" s="12"/>
+      <c r="Q77" s="12"/>
       <c r="S77" s="10">
         <f>SUM(B65:B76)</f>
         <v>12663</v>
@@ -4357,27 +4351,27 @@
         <v>0</v>
       </c>
       <c r="AD77" s="10">
-        <f t="shared" ref="AD77" si="8">U77-D77</f>
+        <f t="shared" ref="AD77" si="11">U77-D77</f>
         <v>0</v>
       </c>
       <c r="AE77" s="10">
-        <f t="shared" ref="AE77" si="9">V77-E77</f>
+        <f t="shared" ref="AE77" si="12">V77-E77</f>
         <v>0</v>
       </c>
       <c r="AF77" s="10">
-        <f t="shared" ref="AF77" si="10">W77-G77</f>
+        <f t="shared" ref="AF77" si="13">W77-G77</f>
         <v>0</v>
       </c>
       <c r="AG77" s="10">
-        <f t="shared" ref="AG77" si="11">X77-H77</f>
+        <f t="shared" ref="AG77" si="14">X77-H77</f>
         <v>0</v>
       </c>
       <c r="AH77" s="10">
-        <f t="shared" ref="AH77" si="12">Y77-I77</f>
+        <f t="shared" ref="AH77" si="15">Y77-I77</f>
         <v>0</v>
       </c>
       <c r="AI77" s="10">
-        <f t="shared" ref="AI77" si="13">Z77-J77</f>
+        <f t="shared" ref="AI77" si="16">Z77-J77</f>
         <v>0</v>
       </c>
     </row>
@@ -4397,7 +4391,7 @@
       <c r="E78" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="F78" s="14"/>
+      <c r="F78" s="9"/>
       <c r="G78" s="9" t="s">
         <v>76</v>
       </c>
@@ -4410,13 +4404,13 @@
       <c r="J78" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="K78" s="14"/>
-      <c r="L78" s="16"/>
-      <c r="M78" s="16"/>
-      <c r="N78" s="14"/>
-      <c r="O78" s="14"/>
-      <c r="P78" s="14"/>
-      <c r="Q78" s="14"/>
+      <c r="K78" s="9"/>
+      <c r="L78" s="13"/>
+      <c r="M78" s="13"/>
+      <c r="N78" s="9"/>
+      <c r="O78" s="9"/>
+      <c r="P78" s="9"/>
+      <c r="Q78" s="9"/>
     </row>
     <row r="79" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="3" t="s">
@@ -4434,7 +4428,7 @@
       <c r="E79" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="F79" s="14"/>
+      <c r="F79" s="9"/>
       <c r="G79" s="9" t="s">
         <v>76</v>
       </c>
@@ -4447,13 +4441,13 @@
       <c r="J79" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="K79" s="14"/>
-      <c r="L79" s="16"/>
-      <c r="M79" s="16"/>
-      <c r="N79" s="14"/>
-      <c r="O79" s="14"/>
-      <c r="P79" s="14"/>
-      <c r="Q79" s="14"/>
+      <c r="K79" s="9"/>
+      <c r="L79" s="13"/>
+      <c r="M79" s="13"/>
+      <c r="N79" s="9"/>
+      <c r="O79" s="9"/>
+      <c r="P79" s="9"/>
+      <c r="Q79" s="9"/>
     </row>
     <row r="80" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="3" t="s">
@@ -4471,7 +4465,7 @@
       <c r="E80" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="F80" s="14"/>
+      <c r="F80" s="9"/>
       <c r="G80" s="9" t="s">
         <v>76</v>
       </c>
@@ -4484,13 +4478,13 @@
       <c r="J80" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="K80" s="14"/>
-      <c r="L80" s="16"/>
-      <c r="M80" s="16"/>
-      <c r="N80" s="14"/>
-      <c r="O80" s="14"/>
-      <c r="P80" s="14"/>
-      <c r="Q80" s="14"/>
+      <c r="K80" s="9"/>
+      <c r="L80" s="13"/>
+      <c r="M80" s="13"/>
+      <c r="N80" s="9"/>
+      <c r="O80" s="9"/>
+      <c r="P80" s="9"/>
+      <c r="Q80" s="9"/>
     </row>
     <row r="81" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="3" t="s">
@@ -4508,7 +4502,7 @@
       <c r="E81" s="4">
         <v>8265</v>
       </c>
-      <c r="F81" s="12"/>
+      <c r="F81" s="4"/>
       <c r="G81" s="4">
         <v>1183</v>
       </c>
@@ -4521,19 +4515,19 @@
       <c r="J81" s="4">
         <v>5778</v>
       </c>
-      <c r="K81" s="12"/>
-      <c r="L81" s="16">
-        <f>B81/C81-1.05</f>
+      <c r="K81" s="4"/>
+      <c r="L81" s="13">
+        <f t="shared" ref="L81:L87" si="17">B81/C81-1.05</f>
         <v>8.877644894204284E-3</v>
       </c>
-      <c r="M81" s="16">
+      <c r="M81" s="13">
         <f>D81/E81-1.05</f>
         <v>2.2111312764670155E-2</v>
       </c>
-      <c r="N81" s="12"/>
-      <c r="O81" s="12"/>
-      <c r="P81" s="12"/>
-      <c r="Q81" s="12"/>
+      <c r="N81" s="4"/>
+      <c r="O81" s="4"/>
+      <c r="P81" s="4"/>
+      <c r="Q81" s="4"/>
     </row>
     <row r="82" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="3" t="s">
@@ -4551,7 +4545,7 @@
       <c r="E82" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="F82" s="12"/>
+      <c r="F82" s="4"/>
       <c r="G82" s="4">
         <v>192</v>
       </c>
@@ -4564,16 +4558,16 @@
       <c r="J82" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="K82" s="12"/>
-      <c r="L82" s="16">
-        <f>B82/C82-1.05</f>
+      <c r="K82" s="4"/>
+      <c r="L82" s="13">
+        <f t="shared" si="17"/>
         <v>1.2820512820512775E-3</v>
       </c>
-      <c r="M82" s="16"/>
-      <c r="N82" s="12"/>
-      <c r="O82" s="12"/>
-      <c r="P82" s="12"/>
-      <c r="Q82" s="12"/>
+      <c r="M82" s="13"/>
+      <c r="N82" s="4"/>
+      <c r="O82" s="4"/>
+      <c r="P82" s="4"/>
+      <c r="Q82" s="4"/>
     </row>
     <row r="83" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="3" t="s">
@@ -4591,7 +4585,7 @@
       <c r="E83" s="4">
         <v>33980</v>
       </c>
-      <c r="F83" s="12"/>
+      <c r="F83" s="4"/>
       <c r="G83" s="4">
         <v>1357</v>
       </c>
@@ -4604,19 +4598,19 @@
       <c r="J83" s="4">
         <v>28870</v>
       </c>
-      <c r="K83" s="12"/>
-      <c r="L83" s="16">
-        <f>B83/C83-1.05</f>
+      <c r="K83" s="4"/>
+      <c r="L83" s="13">
+        <f t="shared" si="17"/>
         <v>2.6984763432237324E-2</v>
       </c>
-      <c r="M83" s="16">
+      <c r="M83" s="13">
         <f>D83/E83-1.05</f>
         <v>-5.7680988816950496E-3</v>
       </c>
-      <c r="N83" s="12"/>
-      <c r="O83" s="12"/>
-      <c r="P83" s="12"/>
-      <c r="Q83" s="12"/>
+      <c r="N83" s="4"/>
+      <c r="O83" s="4"/>
+      <c r="P83" s="4"/>
+      <c r="Q83" s="4"/>
     </row>
     <row r="84" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="3" t="s">
@@ -4634,7 +4628,7 @@
       <c r="E84" s="4">
         <v>27175</v>
       </c>
-      <c r="F84" s="12"/>
+      <c r="F84" s="4"/>
       <c r="G84" s="4">
         <v>2410</v>
       </c>
@@ -4647,19 +4641,19 @@
       <c r="J84" s="4">
         <v>14877</v>
       </c>
-      <c r="K84" s="12"/>
-      <c r="L84" s="16">
-        <f>B84/C84-1.05</f>
+      <c r="K84" s="4"/>
+      <c r="L84" s="13">
+        <f t="shared" si="17"/>
         <v>-2.3228346456692917E-2</v>
       </c>
-      <c r="M84" s="16">
+      <c r="M84" s="13">
         <f>D84/E84-1.05</f>
         <v>-1.6182152713891451E-2</v>
       </c>
-      <c r="N84" s="12"/>
-      <c r="O84" s="12"/>
-      <c r="P84" s="12"/>
-      <c r="Q84" s="12"/>
+      <c r="N84" s="4"/>
+      <c r="O84" s="4"/>
+      <c r="P84" s="4"/>
+      <c r="Q84" s="4"/>
     </row>
     <row r="85" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="3" t="s">
@@ -4677,7 +4671,7 @@
       <c r="E85" s="4">
         <v>2986</v>
       </c>
-      <c r="F85" s="12"/>
+      <c r="F85" s="4"/>
       <c r="G85" s="4">
         <v>122</v>
       </c>
@@ -4690,19 +4684,19 @@
       <c r="J85" s="4">
         <v>2065</v>
       </c>
-      <c r="K85" s="12"/>
-      <c r="L85" s="16">
-        <f>B85/C85-1.05</f>
+      <c r="K85" s="4"/>
+      <c r="L85" s="13">
+        <f t="shared" si="17"/>
         <v>-7.439024390243909E-2</v>
       </c>
-      <c r="M85" s="16">
+      <c r="M85" s="13">
         <f>D85/E85-1.05</f>
         <v>-4.8660415271265967E-2</v>
       </c>
-      <c r="N85" s="12"/>
-      <c r="O85" s="12"/>
-      <c r="P85" s="12"/>
-      <c r="Q85" s="12"/>
+      <c r="N85" s="4"/>
+      <c r="O85" s="4"/>
+      <c r="P85" s="4"/>
+      <c r="Q85" s="4"/>
     </row>
     <row r="86" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="5" t="s">
@@ -4720,7 +4714,7 @@
       <c r="E86" s="6">
         <v>72406</v>
       </c>
-      <c r="F86" s="13"/>
+      <c r="F86" s="12"/>
       <c r="G86" s="6">
         <v>5264</v>
       </c>
@@ -4733,19 +4727,19 @@
       <c r="J86" s="6">
         <v>51590</v>
       </c>
-      <c r="K86" s="13"/>
-      <c r="L86" s="16">
-        <f>B86/C86-1.05</f>
+      <c r="K86" s="12"/>
+      <c r="L86" s="13">
+        <f t="shared" si="17"/>
         <v>-4.783621191538856E-3</v>
       </c>
-      <c r="M86" s="16">
+      <c r="M86" s="13">
         <f>D86/E86-1.05</f>
         <v>-8.2631273651354586E-3</v>
       </c>
-      <c r="N86" s="13"/>
-      <c r="O86" s="13"/>
-      <c r="P86" s="13"/>
-      <c r="Q86" s="13"/>
+      <c r="N86" s="12"/>
+      <c r="O86" s="12"/>
+      <c r="P86" s="12"/>
+      <c r="Q86" s="12"/>
       <c r="S86" s="10">
         <f>SUM(B78:B85)</f>
         <v>5386</v>
@@ -4787,27 +4781,27 @@
         <v>0</v>
       </c>
       <c r="AD86" s="10">
-        <f t="shared" ref="AD86" si="14">U86-D86</f>
+        <f t="shared" ref="AD86" si="18">U86-D86</f>
         <v>0</v>
       </c>
       <c r="AE86" s="10">
-        <f t="shared" ref="AE86" si="15">V86-E86</f>
+        <f t="shared" ref="AE86" si="19">V86-E86</f>
         <v>0</v>
       </c>
       <c r="AF86" s="10">
-        <f t="shared" ref="AF86" si="16">W86-G86</f>
+        <f t="shared" ref="AF86" si="20">W86-G86</f>
         <v>0</v>
       </c>
       <c r="AG86" s="10">
-        <f t="shared" ref="AG86" si="17">X86-H86</f>
+        <f t="shared" ref="AG86" si="21">X86-H86</f>
         <v>0</v>
       </c>
       <c r="AH86" s="10">
-        <f t="shared" ref="AH86" si="18">Y86-I86</f>
+        <f t="shared" ref="AH86" si="22">Y86-I86</f>
         <v>0</v>
       </c>
       <c r="AI86" s="10">
-        <f t="shared" ref="AI86" si="19">Z86-J86</f>
+        <f t="shared" ref="AI86" si="23">Z86-J86</f>
         <v>0</v>
       </c>
     </row>
@@ -4827,7 +4821,7 @@
       <c r="E87" s="4">
         <v>4750</v>
       </c>
-      <c r="F87" s="12"/>
+      <c r="F87" s="4"/>
       <c r="G87" s="4">
         <v>1144</v>
       </c>
@@ -4840,19 +4834,19 @@
       <c r="J87" s="4">
         <v>4491</v>
       </c>
-      <c r="K87" s="12"/>
-      <c r="L87" s="16">
-        <f>B87/C87-1.05</f>
+      <c r="K87" s="4"/>
+      <c r="L87" s="13">
+        <f t="shared" si="17"/>
         <v>2.6592082616178958E-2</v>
       </c>
-      <c r="M87" s="17">
+      <c r="M87" s="14">
         <f>D87/E87-1.05</f>
         <v>9.4210526315789522E-2</v>
       </c>
-      <c r="N87" s="12"/>
-      <c r="O87" s="12"/>
-      <c r="P87" s="12"/>
-      <c r="Q87" s="12"/>
+      <c r="N87" s="4"/>
+      <c r="O87" s="4"/>
+      <c r="P87" s="4"/>
+      <c r="Q87" s="4"/>
     </row>
     <row r="88" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="3" t="s">
@@ -4870,7 +4864,7 @@
       <c r="E88" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="F88" s="14"/>
+      <c r="F88" s="9"/>
       <c r="G88" s="9" t="s">
         <v>76</v>
       </c>
@@ -4883,13 +4877,13 @@
       <c r="J88" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="K88" s="14"/>
-      <c r="L88" s="16"/>
-      <c r="M88" s="16"/>
-      <c r="N88" s="14"/>
-      <c r="O88" s="14"/>
-      <c r="P88" s="14"/>
-      <c r="Q88" s="14"/>
+      <c r="K88" s="9"/>
+      <c r="L88" s="13"/>
+      <c r="M88" s="13"/>
+      <c r="N88" s="9"/>
+      <c r="O88" s="9"/>
+      <c r="P88" s="9"/>
+      <c r="Q88" s="9"/>
     </row>
     <row r="89" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="3" t="s">
@@ -4907,7 +4901,7 @@
       <c r="E89" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="F89" s="14"/>
+      <c r="F89" s="9"/>
       <c r="G89" s="9" t="s">
         <v>76</v>
       </c>
@@ -4920,13 +4914,13 @@
       <c r="J89" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="K89" s="14"/>
-      <c r="L89" s="16"/>
-      <c r="M89" s="16"/>
-      <c r="N89" s="14"/>
-      <c r="O89" s="14"/>
-      <c r="P89" s="14"/>
-      <c r="Q89" s="14"/>
+      <c r="K89" s="9"/>
+      <c r="L89" s="13"/>
+      <c r="M89" s="13"/>
+      <c r="N89" s="9"/>
+      <c r="O89" s="9"/>
+      <c r="P89" s="9"/>
+      <c r="Q89" s="9"/>
     </row>
     <row r="90" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="3" t="s">
@@ -4944,7 +4938,7 @@
       <c r="E90" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="F90" s="14"/>
+      <c r="F90" s="9"/>
       <c r="G90" s="9" t="s">
         <v>76</v>
       </c>
@@ -4957,13 +4951,13 @@
       <c r="J90" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="K90" s="14"/>
-      <c r="L90" s="16"/>
-      <c r="M90" s="16"/>
-      <c r="N90" s="14"/>
-      <c r="O90" s="14"/>
-      <c r="P90" s="14"/>
-      <c r="Q90" s="14"/>
+      <c r="K90" s="9"/>
+      <c r="L90" s="13"/>
+      <c r="M90" s="13"/>
+      <c r="N90" s="9"/>
+      <c r="O90" s="9"/>
+      <c r="P90" s="9"/>
+      <c r="Q90" s="9"/>
     </row>
     <row r="91" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="3" t="s">
@@ -4981,7 +4975,7 @@
       <c r="E91" s="4">
         <v>3519</v>
       </c>
-      <c r="F91" s="12"/>
+      <c r="F91" s="4"/>
       <c r="G91" s="4">
         <v>487</v>
       </c>
@@ -4994,19 +4988,19 @@
       <c r="J91" s="4">
         <v>2532</v>
       </c>
-      <c r="K91" s="12"/>
-      <c r="L91" s="16">
+      <c r="K91" s="4"/>
+      <c r="L91" s="13">
         <f>B91/C91-1.05</f>
         <v>2.4438202247190954E-2</v>
       </c>
-      <c r="M91" s="17">
+      <c r="M91" s="14">
         <f>D91/E91-1.05</f>
         <v>0.14977266268826361</v>
       </c>
-      <c r="N91" s="12"/>
-      <c r="O91" s="12"/>
-      <c r="P91" s="12"/>
-      <c r="Q91" s="12"/>
+      <c r="N91" s="4"/>
+      <c r="O91" s="4"/>
+      <c r="P91" s="4"/>
+      <c r="Q91" s="4"/>
     </row>
     <row r="92" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" s="3" t="s">
@@ -5024,7 +5018,7 @@
       <c r="E92" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="F92" s="14"/>
+      <c r="F92" s="9"/>
       <c r="G92" s="9" t="s">
         <v>76</v>
       </c>
@@ -5037,13 +5031,13 @@
       <c r="J92" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="K92" s="14"/>
-      <c r="L92" s="16"/>
-      <c r="M92" s="16"/>
-      <c r="N92" s="14"/>
-      <c r="O92" s="14"/>
-      <c r="P92" s="14"/>
-      <c r="Q92" s="14"/>
+      <c r="K92" s="9"/>
+      <c r="L92" s="13"/>
+      <c r="M92" s="13"/>
+      <c r="N92" s="9"/>
+      <c r="O92" s="9"/>
+      <c r="P92" s="9"/>
+      <c r="Q92" s="9"/>
     </row>
     <row r="93" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="3" t="s">
@@ -5061,7 +5055,7 @@
       <c r="E93" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="F93" s="14"/>
+      <c r="F93" s="9"/>
       <c r="G93" s="9" t="s">
         <v>76</v>
       </c>
@@ -5074,13 +5068,13 @@
       <c r="J93" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="K93" s="14"/>
-      <c r="L93" s="16"/>
-      <c r="M93" s="16"/>
-      <c r="N93" s="14"/>
-      <c r="O93" s="14"/>
-      <c r="P93" s="14"/>
-      <c r="Q93" s="14"/>
+      <c r="K93" s="9"/>
+      <c r="L93" s="13"/>
+      <c r="M93" s="13"/>
+      <c r="N93" s="9"/>
+      <c r="O93" s="9"/>
+      <c r="P93" s="9"/>
+      <c r="Q93" s="9"/>
     </row>
     <row r="94" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="3" t="s">
@@ -5098,7 +5092,7 @@
       <c r="E94" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="F94" s="14"/>
+      <c r="F94" s="9"/>
       <c r="G94" s="9" t="s">
         <v>76</v>
       </c>
@@ -5111,13 +5105,13 @@
       <c r="J94" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="K94" s="14"/>
-      <c r="L94" s="16"/>
-      <c r="M94" s="16"/>
-      <c r="N94" s="14"/>
-      <c r="O94" s="14"/>
-      <c r="P94" s="14"/>
-      <c r="Q94" s="14"/>
+      <c r="K94" s="9"/>
+      <c r="L94" s="13"/>
+      <c r="M94" s="13"/>
+      <c r="N94" s="9"/>
+      <c r="O94" s="9"/>
+      <c r="P94" s="9"/>
+      <c r="Q94" s="9"/>
     </row>
     <row r="95" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" s="3" t="s">
@@ -5135,7 +5129,7 @@
       <c r="E95" s="4">
         <v>2005</v>
       </c>
-      <c r="F95" s="12"/>
+      <c r="F95" s="4"/>
       <c r="G95" s="4">
         <v>76</v>
       </c>
@@ -5148,19 +5142,19 @@
       <c r="J95" s="4">
         <v>1279</v>
       </c>
-      <c r="K95" s="12"/>
-      <c r="L95" s="17">
+      <c r="K95" s="4"/>
+      <c r="L95" s="14">
         <f>B95/C95-1.05</f>
         <v>0.26132075471698113</v>
       </c>
-      <c r="M95" s="16">
+      <c r="M95" s="13">
         <f>D95/E95-1.05</f>
         <v>5.8728179551122084E-2</v>
       </c>
-      <c r="N95" s="12"/>
-      <c r="O95" s="12"/>
-      <c r="P95" s="12"/>
-      <c r="Q95" s="12"/>
+      <c r="N95" s="4"/>
+      <c r="O95" s="4"/>
+      <c r="P95" s="4"/>
+      <c r="Q95" s="4"/>
     </row>
     <row r="96" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="3" t="s">
@@ -5178,7 +5172,7 @@
       <c r="E96" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="F96" s="14"/>
+      <c r="F96" s="9"/>
       <c r="G96" s="4">
         <v>93</v>
       </c>
@@ -5191,16 +5185,16 @@
       <c r="J96" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="K96" s="14"/>
-      <c r="L96" s="17">
+      <c r="K96" s="9"/>
+      <c r="L96" s="14">
         <f>B96/C96-1.05</f>
         <v>0.17999999999999994</v>
       </c>
-      <c r="M96" s="16"/>
-      <c r="N96" s="14"/>
-      <c r="O96" s="14"/>
-      <c r="P96" s="14"/>
-      <c r="Q96" s="14"/>
+      <c r="M96" s="13"/>
+      <c r="N96" s="9"/>
+      <c r="O96" s="9"/>
+      <c r="P96" s="9"/>
+      <c r="Q96" s="9"/>
     </row>
     <row r="97" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" s="5" t="s">
@@ -5218,7 +5212,7 @@
       <c r="E97" s="6">
         <v>10274</v>
       </c>
-      <c r="F97" s="13"/>
+      <c r="F97" s="12"/>
       <c r="G97" s="6">
         <v>1800</v>
       </c>
@@ -5231,19 +5225,19 @@
       <c r="J97" s="6">
         <v>8302</v>
       </c>
-      <c r="K97" s="13"/>
-      <c r="L97" s="16">
+      <c r="K97" s="12"/>
+      <c r="L97" s="13">
         <f>B97/C97-1.05</f>
         <v>4.5192307692307754E-2</v>
       </c>
-      <c r="M97" s="16">
+      <c r="M97" s="13">
         <f>D97/E97-1.05</f>
         <v>0.10631691648822272</v>
       </c>
-      <c r="N97" s="13"/>
-      <c r="O97" s="13"/>
-      <c r="P97" s="13"/>
-      <c r="Q97" s="13"/>
+      <c r="N97" s="12"/>
+      <c r="O97" s="12"/>
+      <c r="P97" s="12"/>
+      <c r="Q97" s="12"/>
       <c r="S97" s="10">
         <f>SUM(B87:B96)</f>
         <v>2278</v>
@@ -5285,27 +5279,27 @@
         <v>0</v>
       </c>
       <c r="AD97" s="10">
-        <f t="shared" ref="AD97:AD99" si="20">U97-D97</f>
+        <f t="shared" ref="AD97:AD99" si="24">U97-D97</f>
         <v>0</v>
       </c>
       <c r="AE97" s="10">
-        <f t="shared" ref="AE97:AE99" si="21">V97-E97</f>
+        <f t="shared" ref="AE97:AE99" si="25">V97-E97</f>
         <v>0</v>
       </c>
       <c r="AF97" s="10">
-        <f t="shared" ref="AF97:AF99" si="22">W97-G97</f>
+        <f t="shared" ref="AF97:AF99" si="26">W97-G97</f>
         <v>0</v>
       </c>
       <c r="AG97" s="10">
-        <f t="shared" ref="AG97:AG99" si="23">X97-H97</f>
+        <f t="shared" ref="AG97:AG99" si="27">X97-H97</f>
         <v>0</v>
       </c>
       <c r="AH97" s="10">
-        <f t="shared" ref="AH97:AH99" si="24">Y97-I97</f>
+        <f t="shared" ref="AH97:AH99" si="28">Y97-I97</f>
         <v>0</v>
       </c>
       <c r="AI97" s="10">
-        <f t="shared" ref="AI97:AI99" si="25">Z97-J97</f>
+        <f t="shared" ref="AI97:AI99" si="29">Z97-J97</f>
         <v>0</v>
       </c>
     </row>
@@ -5325,7 +5319,7 @@
       <c r="E98" s="6">
         <v>194766</v>
       </c>
-      <c r="F98" s="13"/>
+      <c r="F98" s="12"/>
       <c r="G98" s="6">
         <v>15856</v>
       </c>
@@ -5338,49 +5332,49 @@
       <c r="J98" s="6">
         <v>127276</v>
       </c>
-      <c r="K98" s="13"/>
-      <c r="L98" s="16">
+      <c r="K98" s="12"/>
+      <c r="L98" s="13">
         <f>B98/C98-1.05</f>
         <v>2.8412647885829534E-2</v>
       </c>
-      <c r="M98" s="16">
+      <c r="M98" s="13">
         <f>D98/E98-1.05</f>
         <v>3.8326504626064128E-2</v>
       </c>
-      <c r="N98" s="13"/>
-      <c r="O98" s="13"/>
-      <c r="P98" s="13"/>
-      <c r="Q98" s="13"/>
+      <c r="N98" s="12"/>
+      <c r="O98" s="12"/>
+      <c r="P98" s="12"/>
+      <c r="Q98" s="12"/>
       <c r="S98" s="10">
         <f>SUM(S77:S97)</f>
         <v>20327</v>
       </c>
       <c r="T98" s="10">
-        <f t="shared" ref="T98:Z98" si="26">SUM(T77:T97)</f>
+        <f t="shared" ref="T98:Z98" si="30">SUM(T77:T97)</f>
         <v>18849</v>
       </c>
       <c r="U98" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>211969</v>
       </c>
       <c r="V98" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>194767</v>
       </c>
       <c r="W98" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>15856</v>
       </c>
       <c r="X98" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>13571</v>
       </c>
       <c r="Y98" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>141435</v>
       </c>
       <c r="Z98" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>127276</v>
       </c>
       <c r="AB98" s="10">
@@ -5392,27 +5386,27 @@
         <v>0</v>
       </c>
       <c r="AD98" s="10">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AE98" s="10">
-        <f t="shared" si="21"/>
-        <v>1</v>
-      </c>
-      <c r="AF98" s="10">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AG98" s="10">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH98" s="10">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
+      <c r="AE98" s="10">
+        <f t="shared" si="25"/>
+        <v>1</v>
+      </c>
+      <c r="AF98" s="10">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AG98" s="10">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH98" s="10">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AI98" s="10">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
     </row>
@@ -5432,7 +5426,7 @@
       <c r="E99" s="6">
         <v>2098613</v>
       </c>
-      <c r="F99" s="13"/>
+      <c r="F99" s="12"/>
       <c r="G99" s="6">
         <v>188653</v>
       </c>
@@ -5445,49 +5439,49 @@
       <c r="J99" s="6">
         <v>1367503</v>
       </c>
-      <c r="K99" s="13"/>
-      <c r="L99" s="16">
+      <c r="K99" s="12"/>
+      <c r="L99" s="13">
         <f>B99/C99-1.05</f>
         <v>3.8525680619565739E-2</v>
       </c>
-      <c r="M99" s="16">
+      <c r="M99" s="13">
         <f>D99/E99-1.05</f>
         <v>-1.5660343283885325E-4</v>
       </c>
-      <c r="N99" s="13"/>
-      <c r="O99" s="13"/>
-      <c r="P99" s="13"/>
-      <c r="Q99" s="13"/>
+      <c r="N99" s="12"/>
+      <c r="O99" s="12"/>
+      <c r="P99" s="12"/>
+      <c r="Q99" s="12"/>
       <c r="S99" s="10">
         <f>S98+S64</f>
         <v>229102</v>
       </c>
       <c r="T99" s="10">
-        <f t="shared" ref="T99:Z99" si="27">T98+T64</f>
+        <f t="shared" ref="T99:Z99" si="31">T98+T64</f>
         <v>210476</v>
       </c>
       <c r="U99" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>2203215</v>
       </c>
       <c r="V99" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>2098657</v>
       </c>
       <c r="W99" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>188653</v>
       </c>
       <c r="X99" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>159903</v>
       </c>
       <c r="Y99" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>1441336</v>
       </c>
       <c r="Z99" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>1367663</v>
       </c>
       <c r="AB99" s="10">
@@ -5499,27 +5493,27 @@
         <v>6</v>
       </c>
       <c r="AD99" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AE99" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>44</v>
       </c>
       <c r="AF99" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AG99" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>35</v>
       </c>
       <c r="AH99" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>54</v>
       </c>
       <c r="AI99" s="10">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>160</v>
       </c>
     </row>
